--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/maule.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M247"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30204.74</v>
+        <v>29948.92</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4274.89</v>
+        <v>4232.22</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3051.89</v>
+        <v>3021.44</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>13306.74</v>
+        <v>13173.93</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>22643.91</v>
+        <v>22406.78</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>8076.6</v>
+        <v>7992.02</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>24522.29</v>
+        <v>24265.49</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>39922.24</v>
+        <v>39704.03</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>13542.84</v>
+        <v>13391.95</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>19475.51</v>
+        <v>19258.52</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23351.56</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1739.79</v>
+        <v>1730.27</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>9061.42</v>
+        <v>9049.889999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1599.43</v>
+        <v>1597.39</v>
       </c>
     </row>
     <row r="16">
@@ -1427,7 +1427,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>28652.27</v>
+        <v>28615.8</v>
       </c>
     </row>
     <row r="17">
@@ -1488,7 +1488,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>2137.43</v>
+        <v>2134.71</v>
       </c>
     </row>
     <row r="18">
@@ -1549,7 +1549,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2233.63</v>
+        <v>2257.92</v>
       </c>
     </row>
     <row r="19">
@@ -1610,7 +1610,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>641.23</v>
+        <v>648.21</v>
       </c>
     </row>
     <row r="20">
@@ -1671,7 +1671,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>752.38</v>
+        <v>755.88</v>
       </c>
     </row>
     <row r="21">
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5355.63</v>
+        <v>5394.24</v>
       </c>
     </row>
     <row r="22">
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>8382.200000000001</v>
+        <v>8367.33</v>
       </c>
     </row>
     <row r="23">
@@ -1854,7 +1854,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>52449.64</v>
+        <v>52233.47</v>
       </c>
     </row>
     <row r="24">
@@ -1915,7 +1915,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>171.17</v>
+        <v>170.9</v>
       </c>
     </row>
     <row r="25">
@@ -1976,7 +1976,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>267.18</v>
+        <v>266.77</v>
       </c>
     </row>
     <row r="26">
@@ -2037,7 +2037,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>55840.7</v>
+        <v>55754.15</v>
       </c>
     </row>
     <row r="27">
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>564.28</v>
+        <v>563.41</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1681-956-CM25</t>
+          <t>362-554-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>47999.86</v>
+        <v>9108.219999999999</v>
       </c>
     </row>
     <row r="29">
@@ -2220,13 +2220,13 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>36650.28</v>
+        <v>36839.56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>362-554-CM25</t>
+          <t>1681-956-CM25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2281,7 +2281,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>9061.42</v>
+        <v>48247.75</v>
       </c>
     </row>
     <row r="31">
@@ -2342,7 +2342,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>4138.09</v>
+        <v>4159.46</v>
       </c>
     </row>
     <row r="32">
@@ -2403,7 +2403,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>6946.69</v>
+        <v>6982.56</v>
       </c>
     </row>
     <row r="33">
@@ -2468,7 +2468,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>75500.89</v>
+        <v>76033.74000000001</v>
       </c>
     </row>
     <row r="34">
@@ -2529,7 +2529,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>33657.68</v>
+        <v>33895.22</v>
       </c>
     </row>
     <row r="35">
@@ -2590,7 +2590,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>24876.02</v>
+        <v>25051.58</v>
       </c>
     </row>
     <row r="36">
@@ -2651,7 +2651,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>35099.37</v>
+        <v>34645.69</v>
       </c>
     </row>
     <row r="37">
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>15222.39</v>
+        <v>15025.63</v>
       </c>
     </row>
     <row r="38">
@@ -2773,7 +2773,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>1964.72</v>
+        <v>1939.32</v>
       </c>
     </row>
     <row r="39">
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>30848.77</v>
+        <v>30456.92</v>
       </c>
     </row>
     <row r="40">
@@ -2895,7 +2895,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>8248.809999999999</v>
+        <v>8219.23</v>
       </c>
     </row>
     <row r="41">
@@ -2960,7 +2960,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>63052.08</v>
+        <v>62787.75</v>
       </c>
     </row>
     <row r="42">
@@ -3021,13 +3021,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>22133.55</v>
+        <v>22040.76</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057461-8056-CM25</t>
+          <t>1057655-3406-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3082,13 +3082,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>2144.96</v>
+        <v>24088.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057655-3406-CM25</t>
+          <t>1057461-8056-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3113,12 +3113,12 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>24370.53</v>
+        <v>2120.13</v>
       </c>
     </row>
     <row r="45">
@@ -3204,7 +3204,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>90173.22</v>
+        <v>89409.38</v>
       </c>
     </row>
     <row r="46">
@@ -3265,7 +3265,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18058.19</v>
+        <v>17905.23</v>
       </c>
     </row>
     <row r="47">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>9304.92</v>
+        <v>9226.1</v>
       </c>
     </row>
     <row r="48">
@@ -3387,7 +3387,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>27287.72</v>
+        <v>27265.79</v>
       </c>
     </row>
     <row r="49">
@@ -3448,7 +3448,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2171.75</v>
+        <v>2170.01</v>
       </c>
     </row>
     <row r="50">
@@ -3509,7 +3509,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>42265.4</v>
+        <v>42231.43</v>
       </c>
     </row>
     <row r="51">
@@ -3570,7 +3570,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>3274.53</v>
+        <v>3271.9</v>
       </c>
     </row>
     <row r="52">
@@ -3631,7 +3631,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>1091.51</v>
+        <v>1090.63</v>
       </c>
     </row>
     <row r="53">
@@ -3692,7 +3692,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>1200.66</v>
+        <v>1205.27</v>
       </c>
     </row>
     <row r="54">
@@ -3757,7 +3757,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>25400.1</v>
+        <v>25515.21</v>
       </c>
     </row>
     <row r="55">
@@ -3818,7 +3818,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>18610.26</v>
+        <v>18694.59</v>
       </c>
     </row>
     <row r="56">
@@ -3879,7 +3879,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3084.6</v>
+        <v>3098.58</v>
       </c>
     </row>
     <row r="57">
@@ -3944,7 +3944,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>252913.25</v>
+        <v>255074.6</v>
       </c>
     </row>
     <row r="58">
@@ -4005,13 +4005,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8186.32</v>
+        <v>8274.129999999999</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1978-1654-CM25</t>
+          <t>4452-1119-CC25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4031,17 +4031,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4059,20 +4059,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>57031.34</v>
+        <v>63137.51</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>4452-1119-CC25</t>
+          <t>1978-1654-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4092,17 +4096,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4120,24 +4124,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>62336.51</v>
+        <v>57764.17</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1681-1023-CM25</t>
+          <t>1464-8508-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4162,12 +4162,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4192,13 +4192,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>32898.56</v>
+        <v>31017.47</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1464-8508-CM25</t>
+          <t>1681-1023-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4223,12 +4223,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4253,13 +4253,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>30848.77</v>
+        <v>33078.48</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1681-1019-CM25</t>
+          <t>1075337-15571-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4314,13 +4314,13 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>47486.36</v>
+        <v>32472.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1075337-15571-CM25</t>
+          <t>1681-1019-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4345,12 +4345,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -4375,7 +4375,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>32296.33</v>
+        <v>47746.05</v>
       </c>
     </row>
     <row r="65">
@@ -4436,7 +4436,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>33360.09</v>
+        <v>32709.41</v>
       </c>
     </row>
     <row r="66">
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>14469.04</v>
+        <v>14130.56</v>
       </c>
     </row>
     <row r="67">
@@ -4562,7 +4562,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>261145.19</v>
+        <v>257830.51</v>
       </c>
     </row>
     <row r="68">
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>21853.75</v>
+        <v>21576.36</v>
       </c>
     </row>
     <row r="69">
@@ -4684,7 +4684,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>8549.26</v>
+        <v>8440.74</v>
       </c>
     </row>
     <row r="70">
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>24551.57</v>
+        <v>24197.78</v>
       </c>
     </row>
     <row r="71">
@@ -4806,7 +4806,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>3655.96</v>
+        <v>3608.71</v>
       </c>
     </row>
     <row r="72">
@@ -4867,7 +4867,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9591.719999999999</v>
+        <v>9467.75</v>
       </c>
     </row>
     <row r="73">
@@ -4928,7 +4928,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>43310.51</v>
+        <v>43225.21</v>
       </c>
     </row>
     <row r="74">
@@ -4989,7 +4989,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>23659.57</v>
+        <v>23659.72</v>
       </c>
     </row>
     <row r="75">
@@ -5050,7 +5050,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>19302.84</v>
+        <v>19329.64</v>
       </c>
     </row>
     <row r="76">
@@ -5111,7 +5111,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>8997.52</v>
+        <v>8991.370000000001</v>
       </c>
     </row>
     <row r="77">
@@ -5172,13 +5172,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>5571.9</v>
+        <v>5542.47</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1391-175-CM26</t>
+          <t>1391-149-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>678.76</v>
+        <v>2317.54</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1391-149-CM26</t>
+          <t>1391-175-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5294,7 +5294,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>2262.52</v>
+        <v>695.27</v>
       </c>
     </row>
     <row r="80">
@@ -5355,7 +5355,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>59108.63</v>
+        <v>60602.9</v>
       </c>
     </row>
     <row r="81">
@@ -5416,7 +5416,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9050.129999999999</v>
+        <v>9278.91</v>
       </c>
     </row>
     <row r="82">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>3325.13</v>
+        <v>3409.19</v>
       </c>
     </row>
     <row r="83">
@@ -5538,7 +5538,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>44056.8</v>
+        <v>45392.74</v>
       </c>
     </row>
     <row r="84">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>33097.18</v>
+        <v>34100.79</v>
       </c>
     </row>
     <row r="85">
@@ -5664,7 +5664,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>202498.04</v>
+        <v>208638.41</v>
       </c>
     </row>
     <row r="86">
@@ -5725,7 +5725,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>31972.39</v>
+        <v>32941.9</v>
       </c>
     </row>
     <row r="87">
@@ -5786,7 +5786,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>3489.95</v>
+        <v>3593.69</v>
       </c>
     </row>
     <row r="88">
@@ -5847,7 +5847,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>14228.74</v>
+        <v>14651.66</v>
       </c>
     </row>
     <row r="89">
@@ -5908,7 +5908,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>29414.6</v>
+        <v>30288.89</v>
       </c>
     </row>
     <row r="90">
@@ -5969,7 +5969,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>46402.64</v>
+        <v>46237.43</v>
       </c>
     </row>
     <row r="91">
@@ -6030,7 +6030,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>32608.91</v>
+        <v>32492.81</v>
       </c>
     </row>
     <row r="92">
@@ -6091,7 +6091,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>9999.450000000001</v>
+        <v>9924.620000000001</v>
       </c>
     </row>
     <row r="93">
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>25134.96</v>
+        <v>25207.78</v>
       </c>
     </row>
     <row r="94">
@@ -6213,7 +6213,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>28907.1</v>
+        <v>28990.84</v>
       </c>
     </row>
     <row r="95">
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>8766.91</v>
+        <v>8812.190000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6335,7 +6335,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>4332.89</v>
+        <v>4355.28</v>
       </c>
     </row>
     <row r="97">
@@ -6396,7 +6396,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>9835.91</v>
+        <v>9886.719999999999</v>
       </c>
     </row>
     <row r="98">
@@ -6457,7 +6457,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>40585.44</v>
+        <v>40696.86</v>
       </c>
     </row>
     <row r="99">
@@ -6518,7 +6518,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>19761.08</v>
+        <v>19898.66</v>
       </c>
     </row>
     <row r="100">
@@ -6579,7 +6579,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>26449.41</v>
+        <v>26623.61</v>
       </c>
     </row>
     <row r="101">
@@ -6640,13 +6640,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>34825.18</v>
+        <v>34690.76</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>5052-147-SE26</t>
+          <t>1681-159-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6671,12 +6671,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -6694,24 +6694,20 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>302961.85</v>
+        <v>48458.71</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>1681-156-CM26</t>
+          <t>1978-150-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6736,12 +6732,12 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -6766,13 +6762,13 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>37209.6</v>
+        <v>60927.26</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>1978-150-CM26</t>
+          <t>5052-147-SE26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6797,12 +6793,12 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -6820,20 +6816,24 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>60613.44</v>
+        <v>304530.39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1681-159-CM26</t>
+          <t>1681-156-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6888,7 +6888,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>48209.12</v>
+        <v>37402.25</v>
       </c>
     </row>
     <row r="106">
@@ -6949,7 +6949,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>32786.36</v>
+        <v>32817.96</v>
       </c>
     </row>
     <row r="107">
@@ -7010,7 +7010,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9289.469999999999</v>
       </c>
     </row>
     <row r="108">
@@ -7071,7 +7071,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>13989.4</v>
+        <v>14607.2</v>
       </c>
     </row>
     <row r="109">
@@ -7132,13 +7132,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>34480.99</v>
+        <v>36003.74</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1463-104-CM26</t>
+          <t>1142-61-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7193,13 +7193,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8305.65</v>
+        <v>2035.71</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>1462-72-CM26</t>
+          <t>1463-104-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7224,12 +7224,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7254,13 +7254,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>8983.77</v>
+        <v>8546.9</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>1142-61-CM26</t>
+          <t>1462-72-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7315,7 +7315,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>1978.25</v>
+        <v>9244.719999999999</v>
       </c>
     </row>
     <row r="113">
@@ -7376,7 +7376,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>6594.18</v>
+        <v>6620.18</v>
       </c>
     </row>
     <row r="114">
@@ -7437,7 +7437,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5231.04</v>
+        <v>5251.67</v>
       </c>
     </row>
     <row r="115">
@@ -7498,7 +7498,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>29176.78</v>
+        <v>29291.81</v>
       </c>
     </row>
     <row r="116">
@@ -7559,7 +7559,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>22766.45</v>
+        <v>23141.67</v>
       </c>
     </row>
     <row r="117">
@@ -7624,7 +7624,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>240876.54</v>
+        <v>237775.48</v>
       </c>
     </row>
     <row r="118">
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5692.26</v>
+        <v>5618.98</v>
       </c>
     </row>
     <row r="119">
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>41286.42</v>
+        <v>40754.89</v>
       </c>
     </row>
     <row r="120">
@@ -7807,7 +7807,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>16063.57</v>
+        <v>15950.2</v>
       </c>
     </row>
     <row r="121">
@@ -7868,7 +7868,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>24849.07</v>
+        <v>25299.6</v>
       </c>
     </row>
     <row r="122">
@@ -7929,13 +7929,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>7131.68</v>
+        <v>7260.99</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>1738-95-CM26</t>
+          <t>362-195-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7955,17 +7955,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7990,13 +7990,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>23695.09</v>
+        <v>8207.26</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>362-195-CM26</t>
+          <t>1738-95-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8016,17 +8016,17 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -8051,7 +8051,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>8200.190000000001</v>
+        <v>23715.5</v>
       </c>
     </row>
     <row r="125">
@@ -8112,7 +8112,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>33907.77</v>
+        <v>33936.98</v>
       </c>
     </row>
     <row r="126">
@@ -8173,7 +8173,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>1648.54</v>
+        <v>1655.35</v>
       </c>
     </row>
     <row r="127">
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>29485.41</v>
+        <v>29045.62</v>
       </c>
     </row>
     <row r="128">
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>8242.73</v>
+        <v>8123.48</v>
       </c>
     </row>
     <row r="129">
@@ -8356,7 +8356,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>29074.25</v>
+        <v>28448.72</v>
       </c>
     </row>
     <row r="130">
@@ -8417,7 +8417,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>38094.36</v>
+        <v>37274.76</v>
       </c>
     </row>
     <row r="131">
@@ -8478,7 +8478,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>375.87</v>
+        <v>367.78</v>
       </c>
     </row>
     <row r="132">
@@ -8539,7 +8539,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>30988.46</v>
+        <v>30267.39</v>
       </c>
     </row>
     <row r="133">
@@ -8600,7 +8600,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>1099.03</v>
+        <v>1073.46</v>
       </c>
     </row>
     <row r="134">
@@ -8661,7 +8661,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>31061.34</v>
+        <v>30338.57</v>
       </c>
     </row>
     <row r="135">
@@ -8722,7 +8722,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>58192.23</v>
+        <v>56336.66</v>
       </c>
     </row>
     <row r="136">
@@ -8783,13 +8783,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>9249.280000000001</v>
+        <v>8954.35</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1511-416-CM26</t>
+          <t>1057461-450-CM26</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8814,12 +8814,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -8844,7 +8844,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>26969.88</v>
+        <v>28559.97</v>
       </c>
     </row>
     <row r="138">
@@ -8905,13 +8905,13 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>6390.57</v>
+        <v>6264.54</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1057461-450-CM26</t>
+          <t>1511-416-CM26</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -8936,12 +8936,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -8966,13 +8966,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>29134.54</v>
+        <v>26437.99</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1463-157-CM26</t>
+          <t>2046-141-CM26</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -8997,12 +8997,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -9027,13 +9027,13 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>8416.709999999999</v>
+        <v>18822.4</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2046-141-CM26</t>
+          <t>1465-142-CM26</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9058,12 +9058,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9088,13 +9088,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>19331.46</v>
+        <v>14569.51</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1465-142-CM26</t>
+          <t>1463-157-CM26</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9149,7 +9149,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>14963.55</v>
+        <v>8195.07</v>
       </c>
     </row>
     <row r="143">
@@ -9214,7 +9214,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>509807.31</v>
+        <v>500562.02</v>
       </c>
     </row>
     <row r="144">
@@ -9275,7 +9275,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>2689.18</v>
+        <v>2617.17</v>
       </c>
     </row>
     <row r="145">
@@ -9336,7 +9336,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>434.35</v>
+        <v>422.72</v>
       </c>
     </row>
     <row r="146">
@@ -9397,7 +9397,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>8813.48</v>
+        <v>8839.129999999999</v>
       </c>
     </row>
     <row r="147">
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>36289.95</v>
+        <v>36440.77</v>
       </c>
     </row>
     <row r="148">
@@ -9519,7 +9519,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>24425.92</v>
+        <v>24633.23</v>
       </c>
     </row>
     <row r="149">
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>53448.08</v>
+        <v>53358.72</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2436-427-CM26</t>
+          <t>2436-417-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9641,13 +9641,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>40183.27</v>
+        <v>619.53</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2436-426-CM26</t>
+          <t>2436-425-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9702,13 +9702,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>25947.61</v>
+        <v>17263.27</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2436-428-CM26</t>
+          <t>2436-426-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9763,13 +9763,13 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>16979.88</v>
+        <v>26266.95</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2436-417-CM26</t>
+          <t>2436-427-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -9824,13 +9824,13 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>612</v>
+        <v>40677.81</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2436-425-CM26</t>
+          <t>2436-428-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -9885,7 +9885,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>17053.39</v>
+        <v>17188.86</v>
       </c>
     </row>
     <row r="155">
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>135819.44</v>
+        <v>139161.95</v>
       </c>
     </row>
     <row r="156">
@@ -10011,13 +10011,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>206295.33</v>
+        <v>208641.38</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2045-134-CM26</t>
+          <t>1978-349-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10042,12 +10042,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10072,13 +10072,13 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>6682.36</v>
+        <v>58564.41</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1978-349-CM26</t>
+          <t>2045-134-CM26</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -10133,7 +10133,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>58192.23</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="159">
@@ -10194,7 +10194,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8416.709999999999</v>
+        <v>8451.6</v>
       </c>
     </row>
     <row r="160">
@@ -10255,7 +10255,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>38807.87</v>
+        <v>38641.16</v>
       </c>
     </row>
     <row r="161">
@@ -10316,7 +10316,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>33994.84</v>
+        <v>33848.81</v>
       </c>
     </row>
     <row r="162">
@@ -10377,7 +10377,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>30725.29</v>
+        <v>30593.3</v>
       </c>
     </row>
     <row r="163">
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>48984.7</v>
+        <v>48774.27</v>
       </c>
     </row>
     <row r="164">
@@ -10499,7 +10499,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>31476.71</v>
+        <v>31341.49</v>
       </c>
     </row>
     <row r="165">
@@ -10560,13 +10560,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>2344.29</v>
+        <v>2334.22</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1465-172-CM26</t>
+          <t>1057461-642-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10591,12 +10591,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10621,13 +10621,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>13411.3</v>
+        <v>32109.87</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1462-163-CM26</t>
+          <t>1465-172-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10652,12 +10652,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10682,13 +10682,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>9402.76</v>
+        <v>13330.93</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1057461-642-CM26</t>
+          <t>1462-163-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -10743,7 +10743,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>32303.47</v>
+        <v>9346.41</v>
       </c>
     </row>
     <row r="169">
@@ -10804,7 +10804,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>24341.66</v>
+        <v>24010.72</v>
       </c>
     </row>
     <row r="170">
@@ -10865,13 +10865,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>25188.86</v>
+        <v>25324.5</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1057461-672-CM26</t>
+          <t>1075337-8158-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -10926,7 +10926,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1580.97</v>
+        <v>35624.39</v>
       </c>
     </row>
     <row r="172">
@@ -10987,13 +10987,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>3390.9</v>
+        <v>3416.58</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1075337-8158-CM26</t>
+          <t>1057461-672-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11018,12 +11018,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11048,7 +11048,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>35356.58</v>
+        <v>1592.94</v>
       </c>
     </row>
     <row r="174">
@@ -11109,13 +11109,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>11348.84</v>
+        <v>11391.83</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>362-261-CM26</t>
+          <t>2046-229-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11140,12 +11140,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11170,13 +11170,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>9949.389999999999</v>
+        <v>20445.2</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2046-229-CM26</t>
+          <t>362-261-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11201,12 +11201,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11231,7 +11231,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>20496.95</v>
+        <v>9924.27</v>
       </c>
     </row>
     <row r="177">
@@ -11292,7 +11292,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>1007.53</v>
+        <v>1015.04</v>
       </c>
     </row>
     <row r="178">
@@ -11353,7 +11353,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>12773.97</v>
+        <v>12717.98</v>
       </c>
     </row>
     <row r="179">
@@ -11418,7 +11418,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>247715.57</v>
+        <v>247153.3</v>
       </c>
     </row>
     <row r="180">
@@ -11479,7 +11479,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>5558.32</v>
+        <v>5544.6</v>
       </c>
     </row>
     <row r="181">
@@ -11540,13 +11540,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>58208.33</v>
+        <v>58494.26</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2045-172-CM26</t>
+          <t>1075337-8268-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -11601,13 +11601,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7241.23</v>
+        <v>38071.04</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1075337-8268-CM26</t>
+          <t>2045-172-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11632,12 +11632,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11662,13 +11662,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>37945.16</v>
+        <v>7265.25</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1681-394-CM26</t>
+          <t>1469-1396-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11688,17 +11688,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11723,13 +11723,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>36534.09</v>
+        <v>1341.1</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1681-395-CM26</t>
+          <t>1681-394-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11784,13 +11784,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>49918.09</v>
+        <v>36650.37</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1469-1396-CM26</t>
+          <t>1681-395-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11810,17 +11810,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11845,13 +11845,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1336.84</v>
+        <v>50076.96</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>707420-94-CM26</t>
+          <t>1464-800-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11906,13 +11906,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>1303.42</v>
+        <v>31652.84</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1464-800-CM26</t>
+          <t>707420-94-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11937,12 +11937,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11967,7 +11967,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>31485.41</v>
+        <v>1310.35</v>
       </c>
     </row>
     <row r="189">
@@ -12028,7 +12028,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>36673.11</v>
+        <v>37197.87</v>
       </c>
     </row>
     <row r="190">
@@ -12089,7 +12089,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>26386.15</v>
+        <v>26695.67</v>
       </c>
     </row>
     <row r="191">
@@ -12150,7 +12150,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>13283.38</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="192">
@@ -12211,7 +12211,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>8365.49</v>
+        <v>8506.969999999999</v>
       </c>
     </row>
     <row r="193">
@@ -12272,7 +12272,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>1839.66</v>
+        <v>1870.77</v>
       </c>
     </row>
     <row r="194">
@@ -12333,7 +12333,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>14732.3</v>
+        <v>14981.46</v>
       </c>
     </row>
     <row r="195">
@@ -12394,7 +12394,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>8810.629999999999</v>
+        <v>8959.639999999999</v>
       </c>
     </row>
     <row r="196">
@@ -12455,7 +12455,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>683.54</v>
+        <v>690.49</v>
       </c>
     </row>
     <row r="197">
@@ -12516,7 +12516,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>1631.64</v>
+        <v>1648.23</v>
       </c>
     </row>
     <row r="198">
@@ -12577,13 +12577,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>25847.1</v>
+        <v>26089.52</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>4343-197-CM26</t>
+          <t>4343-196-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12638,13 +12638,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>25028.11</v>
+        <v>396.8</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4343-196-CM26</t>
+          <t>4343-197-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12699,7 +12699,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>399.83</v>
+        <v>24838.24</v>
       </c>
     </row>
     <row r="201">
@@ -12760,7 +12760,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>42828.14</v>
+        <v>42104.53</v>
       </c>
     </row>
     <row r="202">
@@ -12825,7 +12825,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>211933.44</v>
+        <v>208925.61</v>
       </c>
     </row>
     <row r="203">
@@ -12886,7 +12886,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>6840.88</v>
+        <v>6746.88</v>
       </c>
     </row>
     <row r="204">
@@ -12947,13 +12947,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>6143.56</v>
+        <v>6105.48</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>2333-333-CM26</t>
+          <t>362-341-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12973,17 +12973,17 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13008,13 +13008,13 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>1992.24</v>
+        <v>8926.379999999999</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>2045-208-CM26</t>
+          <t>707420-101-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13039,12 +13039,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
@@ -13069,13 +13069,13 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>9962.540000000001</v>
+        <v>14740.62</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>707420-101-CM26</t>
+          <t>2045-208-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13100,12 +13100,12 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
@@ -13130,13 +13130,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>14465.6</v>
+        <v>10151.94</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>362-341-CM26</t>
+          <t>2333-333-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13156,17 +13156,17 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -13191,7 +13191,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>8759.84</v>
+        <v>2030.11</v>
       </c>
     </row>
     <row r="209">
@@ -13252,7 +13252,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>60624.03</v>
+        <v>61991.26</v>
       </c>
     </row>
     <row r="210">
@@ -13313,7 +13313,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>3243.8</v>
+        <v>3316.96</v>
       </c>
     </row>
     <row r="211">
@@ -13374,7 +13374,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>36344.7</v>
+        <v>36595.63</v>
       </c>
     </row>
     <row r="212">
@@ -13435,7 +13435,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>19885.54</v>
+        <v>19947.01</v>
       </c>
     </row>
     <row r="213">
@@ -13496,7 +13496,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>5050.21</v>
+        <v>5065.82</v>
       </c>
     </row>
     <row r="214">
@@ -13557,13 +13557,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>54240.48</v>
+        <v>54097.02</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1681-472-CM26</t>
+          <t>1681-471-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -13618,13 +13618,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>35890.06</v>
+        <v>48250.67</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1681-471-CM26</t>
+          <t>1681-472-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -13679,7 +13679,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>48976.3</v>
+        <v>35358.32</v>
       </c>
     </row>
     <row r="217">
@@ -13740,7 +13740,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>32273.09</v>
+        <v>31609.82</v>
       </c>
     </row>
     <row r="218">
@@ -13801,7 +13801,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>111.95</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="219">
@@ -13862,13 +13862,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>36570.39</v>
+        <v>36917.76</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1075337-8782-CM26</t>
+          <t>1465-276-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -13923,13 +13923,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>24479.11</v>
+        <v>15172.85</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1075337-8783-CM26</t>
+          <t>1462-241-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -13954,12 +13954,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -13984,7 +13984,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>6424.84</v>
+        <v>9215.5</v>
       </c>
     </row>
     <row r="222">
@@ -14045,13 +14045,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>8373.950000000001</v>
+        <v>8406.639999999999</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1462-241-CM26</t>
+          <t>1075337-8783-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14076,12 +14076,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -14106,13 +14106,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>9179.66</v>
+        <v>6449.92</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1465-276-CM26</t>
+          <t>1075337-8782-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14137,12 +14137,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -14167,7 +14167,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>15113.86</v>
+        <v>24574.66</v>
       </c>
     </row>
     <row r="225">
@@ -14228,7 +14228,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>859.3200000000001</v>
+        <v>867.96</v>
       </c>
     </row>
     <row r="226">
@@ -14289,7 +14289,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>2736.27</v>
+        <v>2763.79</v>
       </c>
     </row>
     <row r="227">
@@ -14350,18 +14350,18 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>859.3200000000001</v>
+        <v>867.96</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1079566-254-CM26</t>
+          <t>5052-636-SE26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -14376,17 +14376,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SECCIÓN COMPRAS VII ZONA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -14396,28 +14396,32 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
-        </is>
-      </c>
-      <c r="K228" t="inlineStr"/>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>161.12</v>
+        <v>252980.85</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1511-807-CM26</t>
+          <t>1079566-254-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -14437,17 +14441,17 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SECCIÓN COMPRAS VII ZONA</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -14457,12 +14461,12 @@
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K229" t="inlineStr"/>
@@ -14472,18 +14476,18 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>21536.9</v>
+        <v>160.31</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>5052-636-SE26</t>
+          <t>1511-807-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -14503,12 +14507,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -14526,18 +14530,14 @@
           <t>96.781.350-8</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>254268.89</v>
+        <v>21427.81</v>
       </c>
     </row>
     <row r="231">
@@ -14598,7 +14598,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>45608.21</v>
+        <v>45705.41</v>
       </c>
     </row>
     <row r="232">
@@ -14659,7 +14659,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>22172.29</v>
+        <v>22223.14</v>
       </c>
     </row>
     <row r="233">
@@ -14720,7 +14720,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>9081.870000000001</v>
+        <v>9102.700000000001</v>
       </c>
     </row>
     <row r="234">
@@ -14781,7 +14781,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>6315.99</v>
+        <v>6358.27</v>
       </c>
     </row>
     <row r="235">
@@ -14842,7 +14842,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>863.09</v>
+        <v>868.87</v>
       </c>
     </row>
     <row r="236">
@@ -14903,7 +14903,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3158</v>
+        <v>3180.1</v>
       </c>
     </row>
     <row r="237">
@@ -14964,7 +14964,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>3219.37</v>
+        <v>3241.9</v>
       </c>
     </row>
     <row r="238">
@@ -15025,7 +15025,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>19002.09</v>
+        <v>18963.99</v>
       </c>
     </row>
     <row r="239">
@@ -15086,7 +15086,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>33316.62</v>
+        <v>33123.78</v>
       </c>
     </row>
     <row r="240">
@@ -15147,7 +15147,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>258.05</v>
+        <v>253.89</v>
       </c>
     </row>
     <row r="241">
@@ -15208,13 +15208,13 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>37853.96</v>
+        <v>37413.5</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1681-561-CM26</t>
+          <t>1681-560-CM26</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15269,13 +15269,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>38350.71</v>
+        <v>50338.9</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1681-560-CM26</t>
+          <t>1681-561-CM26</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15330,7 +15330,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>50619.53</v>
+        <v>38138.1</v>
       </c>
     </row>
     <row r="244">
@@ -15391,13 +15391,13 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>9130.26</v>
+        <v>9079.639999999999</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1978-787-CM26</t>
+          <t>1978-786-CM26</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15452,13 +15452,13 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>15789.98</v>
+        <v>73324.28</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1978-786-CM26</t>
+          <t>1978-787-CM26</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15513,7 +15513,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>73686.58</v>
+        <v>15712.35</v>
       </c>
     </row>
     <row r="247">
@@ -15574,7 +15574,373 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>37580.16</v>
+        <v>37395.38</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>1057461-1219-CM26</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="n">
+        <v>36596.6</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>1057461-1248-CM26</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="n">
+        <v>7384.46</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>2046-390-CM26</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>61.606.908-k</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="n">
+        <v>21668.62</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>362-455-CM26</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>61.606.915-2</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="n">
+        <v>10344.09</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>2294-1703-CM26</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="n">
+        <v>10494.76</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>1464-1326-CM26</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>61.606.918-7</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="n">
+        <v>37652.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/maule.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M582"/>
+  <dimension ref="A1:M583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -26709,7 +26709,7 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>1681-246-CM26</t>
+          <t>1681-248-CM26</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -26768,13 +26768,13 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>28448.72</v>
+        <v>37274.76</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1681-248-CM26</t>
+          <t>1681-246-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26833,7 +26833,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>37274.76</v>
+        <v>28448.72</v>
       </c>
     </row>
     <row r="407">
@@ -27229,7 +27229,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>2046-141-CM26</t>
+          <t>1463-157-CM26</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -27254,12 +27254,12 @@
       </c>
       <c r="F413" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G413" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H413" t="inlineStr">
@@ -27288,13 +27288,13 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>18822.4</v>
+        <v>8195.07</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1463-157-CM26</t>
+          <t>2046-141-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,12 +27319,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,7 +27353,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>8195.07</v>
+        <v>18822.4</v>
       </c>
     </row>
     <row r="415">
@@ -27489,7 +27489,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1057461-466-CM26</t>
+          <t>707420-54-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27514,12 +27514,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -27548,13 +27548,13 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>2617.17</v>
+        <v>422.72</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>707420-54-CM26</t>
+          <t>1057461-466-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -27579,12 +27579,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -27613,7 +27613,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>422.72</v>
+        <v>2617.17</v>
       </c>
     </row>
     <row r="419">
@@ -28269,7 +28269,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>2045-134-CM26</t>
+          <t>1978-349-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28294,12 +28294,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28328,13 +28328,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>6725.1</v>
+        <v>58564.41</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>1978-349-CM26</t>
+          <t>2045-134-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28359,12 +28359,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>58564.41</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="431">
@@ -29699,7 +29699,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1681-395-CM26</t>
+          <t>1681-394-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29758,13 +29758,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>50076.96</v>
+        <v>36650.37</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1681-394-CM26</t>
+          <t>1681-395-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29823,7 +29823,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>36650.37</v>
+        <v>50076.96</v>
       </c>
     </row>
     <row r="453">
@@ -30609,7 +30609,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>4343-196-CM26</t>
+          <t>4343-197-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30668,13 +30668,13 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>396.8</v>
+        <v>24838.24</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>4343-197-CM26</t>
+          <t>4343-196-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30733,7 +30733,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>24838.24</v>
+        <v>396.8</v>
       </c>
     </row>
     <row r="467">
@@ -31259,7 +31259,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>3876-129-CM26</t>
+          <t>2046-296-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -31279,17 +31279,17 @@
       </c>
       <c r="E475" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F475" t="inlineStr">
         <is>
-          <t>69.100.400-7</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G475" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RAUCO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H475" t="inlineStr">
@@ -31318,13 +31318,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>5065.82</v>
+        <v>19947.01</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>2046-296-CM26</t>
+          <t>3876-129-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -31344,17 +31344,17 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>69.100.400-7</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>I MUNICIPALIDAD DE RAUCO</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -31383,7 +31383,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>19947.01</v>
+        <v>5065.82</v>
       </c>
     </row>
     <row r="477">
@@ -32754,7 +32754,7 @@
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4343-235-CM26</t>
+          <t>1978-730-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32774,17 +32774,17 @@
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -32813,13 +32813,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>3241.9</v>
+        <v>3180.1</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1978-730-CM26</t>
+          <t>4343-235-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32839,17 +32839,17 @@
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -32878,7 +32878,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>3180.1</v>
+        <v>3241.9</v>
       </c>
     </row>
     <row r="500">
@@ -33274,12 +33274,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>1978-787-CM26</t>
+          <t>4452-672-SE26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -33294,17 +33294,17 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -33333,18 +33333,18 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>15712.35</v>
+        <v>159487.73</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>4452-672-SE26</t>
+          <t>1978-786-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -33359,17 +33359,17 @@
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>159487.73</v>
+        <v>73324.28</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1978-786-CM26</t>
+          <t>1978-787-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33463,7 +33463,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>73324.28</v>
+        <v>15712.35</v>
       </c>
     </row>
     <row r="509">
@@ -33534,7 +33534,7 @@
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1057461-1219-CM26</t>
+          <t>1463-278-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33559,12 +33559,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33593,13 +33593,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>36596.6</v>
+        <v>9500.01</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1463-278-CM26</t>
+          <t>1057461-1219-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33624,12 +33624,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -33658,13 +33658,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>9500.01</v>
+        <v>36596.6</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>2335-644-CM26</t>
+          <t>1465-366-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33684,17 +33684,17 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -33723,13 +33723,13 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>378.27</v>
+        <v>14079.24</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2335-645-CM26</t>
+          <t>2335-648-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33788,13 +33788,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>108.44</v>
+        <v>271.09</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2335-646-CM26</t>
+          <t>2335-647-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33853,13 +33853,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>542.1900000000001</v>
+        <v>1084.38</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2335-647-CM26</t>
+          <t>2335-645-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33918,13 +33918,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>1084.38</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>2335-648-CM26</t>
+          <t>2335-644-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33983,13 +33983,13 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>271.09</v>
+        <v>378.27</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>1465-366-CM26</t>
+          <t>2335-646-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -34009,17 +34009,17 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -34048,13 +34048,13 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>14079.24</v>
+        <v>542.1900000000001</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>1057461-1248-CM26</t>
+          <t>1199-185-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -34079,12 +34079,12 @@
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
@@ -34113,13 +34113,13 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>7384.46</v>
+        <v>1766.53</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>1199-185-CM26</t>
+          <t>1057461-1248-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -34144,12 +34144,12 @@
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
@@ -34178,7 +34178,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>1766.53</v>
+        <v>7384.46</v>
       </c>
     </row>
     <row r="520">
@@ -34379,12 +34379,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>4452-746-SE26</t>
+          <t>4343-265-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -34404,12 +34404,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -34438,18 +34438,18 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>28678.33</v>
+        <v>24014.51</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>4343-264-CM26</t>
+          <t>4452-746-SE26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>127.3</v>
+        <v>28678.33</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4343-265-CM26</t>
+          <t>4343-264-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34568,7 +34568,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>24014.51</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="526">
@@ -34639,7 +34639,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1511-991-CM26</t>
+          <t>1511-987-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34698,13 +34698,13 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>92.19</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>1511-990-CM26</t>
+          <t>1511-988-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34769,7 +34769,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>1978-893-CM26</t>
+          <t>1511-989-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34789,17 +34789,17 @@
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -34828,13 +34828,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>1177.1</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1511-988-CM26</t>
+          <t>1511-990-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34899,7 +34899,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>1511-987-CM26</t>
+          <t>1511-991-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -34958,13 +34958,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>214.4</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1511-989-CM26</t>
+          <t>1978-893-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34984,17 +34984,17 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -35023,7 +35023,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>107.2</v>
+        <v>1177.1</v>
       </c>
     </row>
     <row r="533">
@@ -35159,7 +35159,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>2335-677-CM26</t>
+          <t>1681-624-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -35179,17 +35179,17 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -35218,18 +35218,18 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>107.93</v>
+        <v>53236.72</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>4452-779-SE26</t>
+          <t>1681-623-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -35249,12 +35249,12 @@
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -35283,18 +35283,18 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>160327.63</v>
+        <v>39191.68</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>1681-623-CM26</t>
+          <t>5052-637-SE26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -35348,13 +35348,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>39191.68</v>
+        <v>274006.67</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>1681-624-CM26</t>
+          <t>2335-677-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35374,17 +35374,17 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -35413,18 +35413,18 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>53236.72</v>
+        <v>107.93</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>1978-952-CM26</t>
+          <t>4452-779-SE26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -35434,22 +35434,22 @@
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -35478,13 +35478,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>42366.93</v>
+        <v>160327.63</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2294-1703-CM26</t>
+          <t>1978-952-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35504,17 +35504,17 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
@@ -35524,12 +35524,12 @@
       </c>
       <c r="I540" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J540" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K540" t="inlineStr">
@@ -35543,13 +35543,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>10494.76</v>
+        <v>42366.93</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2294-1704-CM26</t>
+          <t>2294-1703-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35608,13 +35608,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>4064.2</v>
+        <v>10494.76</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>2045-298-CM26</t>
+          <t>2294-1704-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -35639,12 +35639,12 @@
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
@@ -35654,12 +35654,12 @@
       </c>
       <c r="I542" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J542" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K542" t="inlineStr">
@@ -35673,13 +35673,13 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>8646.309999999999</v>
+        <v>4064.2</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>1464-1326-CM26</t>
+          <t>2045-298-CM26</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -35694,7 +35694,7 @@
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="E543" t="inlineStr">
@@ -35704,12 +35704,12 @@
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
@@ -35738,7 +35738,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>37652.55</v>
+        <v>8646.309999999999</v>
       </c>
     </row>
     <row r="544">
@@ -35809,7 +35809,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>4605-94-CM26</t>
+          <t>1464-1326-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35834,12 +35834,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>61.819.000-5</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -35868,13 +35868,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>2438.44</v>
+        <v>37652.55</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>1079566-332-CM26</t>
+          <t>4605-94-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35899,12 +35899,12 @@
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.819.000-5</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -35914,12 +35914,12 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>521758.93</v>
+        <v>2438.44</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>1465-445-CM26</t>
+          <t>1079566-332-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35949,12 +35949,12 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="E547" t="inlineStr">
@@ -35964,12 +35964,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35979,12 +35979,12 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
@@ -35998,13 +35998,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>15049.1</v>
+        <v>521758.93</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1057461-1426-CM26</t>
+          <t>1465-445-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -36029,12 +36029,12 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
@@ -36063,13 +36063,13 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>38854.17</v>
+        <v>15049.1</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>362-490-CM26</t>
+          <t>1057461-1426-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -36094,12 +36094,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -36128,13 +36128,13 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>9058.23</v>
+        <v>38854.17</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>3385-204-CM26</t>
+          <t>362-490-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -36149,7 +36149,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -36159,12 +36159,12 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -36193,13 +36193,13 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>524.9</v>
+        <v>9058.23</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>1075337-9601-CM26</t>
+          <t>3385-204-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36224,12 +36224,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -36258,13 +36258,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>29280.54</v>
+        <v>524.9</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>1462-349-CM26</t>
+          <t>1075337-9601-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -36289,12 +36289,12 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -36323,13 +36323,13 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>9231.26</v>
+        <v>29280.54</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>707420-124-CM26</t>
+          <t>1462-349-CM26</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -36354,12 +36354,12 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -36388,13 +36388,13 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>715.15</v>
+        <v>9231.26</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>1463-345-CM26</t>
+          <t>707420-124-CM26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -36409,7 +36409,7 @@
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E554" t="inlineStr">
@@ -36419,12 +36419,12 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -36453,13 +36453,13 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>9655.35</v>
+        <v>715.15</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>1057461-1474-CM26</t>
+          <t>1463-345-CM26</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -36474,7 +36474,7 @@
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E555" t="inlineStr">
@@ -36484,12 +36484,12 @@
       </c>
       <c r="F555" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G555" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H555" t="inlineStr">
@@ -36518,13 +36518,13 @@
         </is>
       </c>
       <c r="M555" s="2" t="n">
-        <v>6182.7</v>
+        <v>9655.35</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1511-1057-CM26</t>
+          <t>1057461-1474-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36549,12 +36549,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36583,13 +36583,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>24839.36</v>
+        <v>6182.7</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2294-1786-CM26</t>
+          <t>2294-1788-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36648,13 +36648,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>32519.85</v>
+        <v>37020.58</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>4343-267-CM26</t>
+          <t>1511-1057-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36679,12 +36679,12 @@
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -36713,13 +36713,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>974.47</v>
+        <v>24839.36</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>2294-1788-CM26</t>
+          <t>4343-267-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36739,17 +36739,17 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -36759,12 +36759,12 @@
       </c>
       <c r="I559" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J559" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K559" t="inlineStr">
@@ -36778,13 +36778,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>37020.58</v>
+        <v>974.47</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2294-1836-CM26</t>
+          <t>2294-1786-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36799,7 +36799,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
@@ -36843,13 +36843,13 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>5051.4</v>
+        <v>32519.85</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>2294-1849-CM26</t>
+          <t>2294-1836-CM26</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -36864,12 +36864,12 @@
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
@@ -36908,13 +36908,13 @@
         </is>
       </c>
       <c r="M561" s="2" t="n">
-        <v>9190.48</v>
+        <v>5051.4</v>
       </c>
     </row>
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>2294-1874-CM26</t>
+          <t>2294-1849-CM26</t>
         </is>
       </c>
       <c r="B562" t="inlineStr">
@@ -36973,13 +36973,13 @@
         </is>
       </c>
       <c r="M562" s="2" t="n">
-        <v>25610.32</v>
+        <v>9190.48</v>
       </c>
     </row>
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>4343-299-CM26</t>
+          <t>2294-1874-CM26</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
@@ -36994,7 +36994,7 @@
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
@@ -37004,12 +37004,12 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -37019,12 +37019,12 @@
       </c>
       <c r="I563" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J563" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K563" t="inlineStr">
@@ -37038,13 +37038,13 @@
         </is>
       </c>
       <c r="M563" s="2" t="n">
-        <v>26871.33</v>
+        <v>25610.32</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>2294-1835-CM26</t>
+          <t>2294-1829-CM26</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
@@ -37103,13 +37103,13 @@
         </is>
       </c>
       <c r="M564" s="2" t="n">
-        <v>17046.98</v>
+        <v>12909.22</v>
       </c>
     </row>
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>4345-13-CM26</t>
+          <t>2294-1834-CM26</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
@@ -37134,12 +37134,12 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -37149,12 +37149,12 @@
       </c>
       <c r="I565" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J565" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K565" t="inlineStr">
@@ -37168,13 +37168,13 @@
         </is>
       </c>
       <c r="M565" s="2" t="n">
-        <v>831.02</v>
+        <v>11339.36</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>2294-1829-CM26</t>
+          <t>2294-1835-CM26</t>
         </is>
       </c>
       <c r="B566" t="inlineStr">
@@ -37233,13 +37233,13 @@
         </is>
       </c>
       <c r="M566" s="2" t="n">
-        <v>12909.22</v>
+        <v>17046.98</v>
       </c>
     </row>
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>2294-1834-CM26</t>
+          <t>4345-13-CM26</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -37264,12 +37264,12 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="I567" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J567" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K567" t="inlineStr">
@@ -37298,13 +37298,13 @@
         </is>
       </c>
       <c r="M567" s="2" t="n">
-        <v>11339.36</v>
+        <v>831.02</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>2046-451-CM26</t>
+          <t>4343-299-CM26</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -37319,7 +37319,7 @@
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
@@ -37329,12 +37329,12 @@
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -37363,18 +37363,18 @@
         </is>
       </c>
       <c r="M568" s="2" t="n">
-        <v>20314.32</v>
+        <v>26871.33</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>4452-844-SE26</t>
+          <t>2046-451-CM26</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C569" t="inlineStr">
@@ -37384,7 +37384,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -37394,12 +37394,12 @@
       </c>
       <c r="F569" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
@@ -37428,18 +37428,18 @@
         </is>
       </c>
       <c r="M569" s="2" t="n">
-        <v>33112.94</v>
+        <v>20314.32</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>2294-1998-CM26</t>
+          <t>4452-844-SE26</t>
         </is>
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C570" t="inlineStr">
@@ -37449,22 +37449,22 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H570" t="inlineStr">
@@ -37474,12 +37474,12 @@
       </c>
       <c r="I570" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J570" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K570" t="inlineStr">
@@ -37493,13 +37493,13 @@
         </is>
       </c>
       <c r="M570" s="2" t="n">
-        <v>4591.25</v>
+        <v>33112.94</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>1142-274-CM26</t>
+          <t>2294-1998-CM26</t>
         </is>
       </c>
       <c r="B571" t="inlineStr">
@@ -37514,22 +37514,22 @@
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -37539,12 +37539,12 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J571" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K571" t="inlineStr">
@@ -37558,7 +37558,7 @@
         </is>
       </c>
       <c r="M571" s="2" t="n">
-        <v>3330.27</v>
+        <v>4591.25</v>
       </c>
     </row>
     <row r="572">
@@ -37694,7 +37694,7 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>696704-83-CM26</t>
+          <t>1142-274-CM26</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -37709,22 +37709,22 @@
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
@@ -37753,13 +37753,13 @@
         </is>
       </c>
       <c r="M574" s="2" t="n">
-        <v>2224.51</v>
+        <v>3330.27</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>1681-713-CM26</t>
+          <t>696704-83-CM26</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -37774,22 +37774,22 @@
       </c>
       <c r="D575" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -37818,7 +37818,7 @@
         </is>
       </c>
       <c r="M575" s="2" t="n">
-        <v>37962.05</v>
+        <v>2224.51</v>
       </c>
     </row>
     <row r="576">
@@ -37889,7 +37889,7 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>1978-1076-CM26</t>
+          <t>1681-713-CM26</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
@@ -37914,12 +37914,12 @@
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
@@ -37948,13 +37948,13 @@
         </is>
       </c>
       <c r="M577" s="2" t="n">
-        <v>55813.86</v>
+        <v>37962.05</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>2045-329-CM26</t>
+          <t>1978-1076-CM26</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
@@ -37969,7 +37969,7 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
@@ -37979,12 +37979,12 @@
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -38013,13 +38013,13 @@
         </is>
       </c>
       <c r="M578" s="2" t="n">
-        <v>8816.51</v>
+        <v>55813.86</v>
       </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>1464-1457-CM26</t>
+          <t>2045-329-CM26</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
@@ -38044,12 +38044,12 @@
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -38078,13 +38078,13 @@
         </is>
       </c>
       <c r="M579" s="2" t="n">
-        <v>30240.64</v>
+        <v>8816.51</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>4452-890-CM26</t>
+          <t>1464-1457-CM26</t>
         </is>
       </c>
       <c r="B580" t="inlineStr">
@@ -38099,22 +38099,22 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H580" t="inlineStr">
@@ -38143,18 +38143,18 @@
         </is>
       </c>
       <c r="M580" s="2" t="n">
-        <v>8598.719999999999</v>
+        <v>30240.64</v>
       </c>
     </row>
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>4452-882-SE26</t>
+          <t>4452-890-CM26</t>
         </is>
       </c>
       <c r="B581" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C581" t="inlineStr">
@@ -38208,71 +38208,136 @@
         </is>
       </c>
       <c r="M581" s="2" t="n">
-        <v>141936.79</v>
+        <v>8598.719999999999</v>
       </c>
     </row>
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
+          <t>4452-882-SE26</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>2239-13-LR23</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J582" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M582" s="2" t="n">
+        <v>141936.79</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
           <t>4452-894-CM26</t>
         </is>
       </c>
-      <c r="B582" t="inlineStr">
+      <c r="B583" t="inlineStr">
         <is>
           <t>2239-1-LR26</t>
         </is>
       </c>
-      <c r="C582" t="inlineStr">
+      <c r="C583" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D582" t="inlineStr">
+      <c r="D583" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="E582" t="inlineStr">
+      <c r="E583" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F582" t="inlineStr">
+      <c r="F583" t="inlineStr">
         <is>
           <t>61.606.903-9</t>
         </is>
       </c>
-      <c r="G582" t="inlineStr">
+      <c r="G583" t="inlineStr">
         <is>
           <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
-      <c r="H582" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I582" t="inlineStr">
-        <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
-        </is>
-      </c>
-      <c r="J582" t="inlineStr">
-        <is>
-          <t>96.781.350-8</t>
-        </is>
-      </c>
-      <c r="K582" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L582" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M582" s="2" t="n">
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J583" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M583" s="2" t="n">
         <v>452.21</v>
       </c>
     </row>

--- a/docs/oc-regiones/administracion-y-entrega-de-beneficios/maule.xlsx
+++ b/docs/oc-regiones/administracion-y-entrega-de-beneficios/maule.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M583"/>
+  <dimension ref="A1:M615"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1034,7 +1034,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3399-3-CM25</t>
+          <t>1057655-2-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1059,12 +1059,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1093,13 +1093,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1974.8</v>
+        <v>18464.22</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1057655-2-CM25</t>
+          <t>3399-3-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>COMANDO DE APOYO A LA FUERZA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1158,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>18464.22</v>
+        <v>1974.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3385-2-CM25</t>
+          <t>3399-2-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1229,7 +1229,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3399-2-CM25</t>
+          <t>3385-2-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1424,7 +1424,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1199-3-CM25</t>
+          <t>3779-7-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.130.401-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1483,13 +1483,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5072.85</v>
+        <v>9830.049999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>3779-5-CM25</t>
+          <t>1199-3-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1509,17 +1509,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.130.401-9</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1548,13 +1548,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>387.31</v>
+        <v>5072.85</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1391-144-CM25</t>
+          <t>3779-5-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1574,17 +1574,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.130.401-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>45655.61</v>
+        <v>387.31</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3779-7-CM25</t>
+          <t>1391-144-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1639,17 +1639,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.130.401-9</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9830.049999999999</v>
+        <v>45655.61</v>
       </c>
     </row>
     <row r="20">
@@ -2139,7 +2139,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3779-17-CM25</t>
+          <t>3399-7-CM25</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.130.401-9</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yerbas Buenas</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2198,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>1791.16</v>
+        <v>3092.18</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1465-79-CM25</t>
+          <t>3779-17-CM25</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2224,17 +2224,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>69.130.401-9</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>Ilustre Municipalidad de Yerbas Buenas</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2263,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>10405.42</v>
+        <v>1791.16</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3399-7-CM25</t>
+          <t>1465-79-CM25</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2328,7 +2328,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3092.18</v>
+        <v>10405.42</v>
       </c>
     </row>
     <row r="30">
@@ -2464,7 +2464,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057461-312-CM25</t>
+          <t>1511-156-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2523,13 +2523,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>24091.21</v>
+        <v>21709.73</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1511-156-CM25</t>
+          <t>1057461-312-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2554,12 +2554,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2588,7 +2588,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>21709.73</v>
+        <v>24091.21</v>
       </c>
     </row>
     <row r="34">
@@ -2984,7 +2984,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>4343-68-CM25</t>
+          <t>4452-181-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3004,17 +3004,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3043,13 +3043,13 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>23175.71</v>
+        <v>19152.81</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>4452-181-CM25</t>
+          <t>4343-68-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3069,17 +3069,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3108,13 +3108,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>19152.81</v>
+        <v>23175.71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1142-48-CM25</t>
+          <t>1681-119-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3139,12 +3139,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3173,13 +3173,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>5057.79</v>
+        <v>205.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1681-119-CM25</t>
+          <t>1142-48-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>205.26</v>
+        <v>5057.79</v>
       </c>
     </row>
     <row r="44">
@@ -3829,7 +3829,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>1462-89-CM25</t>
+          <t>1465-150-CM25</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3888,13 +3888,13 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>7128.48</v>
+        <v>10104.02</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>1057461-2551-CM25</t>
+          <t>3399-28-CM25</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3919,12 +3919,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -3953,13 +3953,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>26290.82</v>
+        <v>948.5</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1465-150-CM25</t>
+          <t>1057461-2551-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10104.02</v>
+        <v>26290.82</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>3399-28-CM25</t>
+          <t>1462-89-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4049,12 +4049,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4083,7 +4083,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>948.5</v>
+        <v>7128.48</v>
       </c>
     </row>
     <row r="57">
@@ -4154,7 +4154,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1391-428-CM25</t>
+          <t>3385-38-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4213,13 +4213,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>214.79</v>
+        <v>3221.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1391-431-CM25</t>
+          <t>1391-428-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4278,13 +4278,13 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3758.87</v>
+        <v>214.79</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>362-118-CM25</t>
+          <t>1391-431-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4343,13 +4343,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>6446.96</v>
+        <v>3758.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3385-38-CM25</t>
+          <t>362-118-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4374,12 +4374,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3221.89</v>
+        <v>6446.96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1391-429-CM25</t>
+          <t>1391-436-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4479,7 +4479,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1391-436-CM25</t>
+          <t>1391-429-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4999,7 +4999,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1391-520-CM25</t>
+          <t>2046-138-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -5058,13 +5058,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1812.24</v>
+        <v>15096.32</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2046-138-CM25</t>
+          <t>1391-520-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5089,12 +5089,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -5123,7 +5123,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>15096.32</v>
+        <v>1812.24</v>
       </c>
     </row>
     <row r="73">
@@ -5454,7 +5454,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1391-535-CM25</t>
+          <t>1391-537-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5513,13 +5513,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>643.6799999999999</v>
+        <v>166.28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1391-537-CM25</t>
+          <t>1391-535-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5578,13 +5578,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>166.28</v>
+        <v>643.6799999999999</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3385-47-CM25</t>
+          <t>3399-53-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5609,7 +5609,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5643,13 +5643,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>32.38</v>
+        <v>3346.2</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3399-53-CM25</t>
+          <t>3385-46-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5708,13 +5708,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>3346.2</v>
+        <v>8635.49</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3385-46-CM25</t>
+          <t>3385-47-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5773,7 +5773,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>8635.49</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="83">
@@ -5974,7 +5974,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1681-255-CM25</t>
+          <t>1978-292-CM25</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5994,17 +5994,17 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -6033,13 +6033,13 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>35871.71</v>
+        <v>71371.08</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1681-256-CM25</t>
+          <t>1681-255-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6098,13 +6098,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>26515.78</v>
+        <v>35871.71</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1335444-8-CM25</t>
+          <t>1681-256-CM25</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6124,17 +6124,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>60.905.000-4</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -6163,13 +6163,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>6704.01</v>
+        <v>26515.78</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1978-292-CM25</t>
+          <t>1335444-8-CM25</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -6194,12 +6194,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>60.905.000-4</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -6228,7 +6228,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>71371.08</v>
+        <v>6704.01</v>
       </c>
     </row>
     <row r="90">
@@ -7534,7 +7534,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>1978-386-CM25</t>
+          <t>1681-334-CM25</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7554,17 +7554,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>35465.15</v>
+        <v>33201.46</v>
       </c>
     </row>
     <row r="111">
@@ -7729,7 +7729,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>1681-334-CM25</t>
+          <t>1978-386-CM25</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7749,17 +7749,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7788,13 +7788,13 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>33201.46</v>
+        <v>35465.15</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>3399-74-CM25</t>
+          <t>1199-129-CM25</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -7859,7 +7859,7 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1199-129-CM25</t>
+          <t>3399-74-CM25</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -7924,7 +7924,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>1467-26-CM25</t>
+          <t>3251-1387-CM25</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -7944,17 +7944,17 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>60.511.071-1</t>
+          <t>69.252.700-3</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
+          <t>I MUNICIPALIDAD DE PELLUHUE</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7983,13 +7983,13 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2796.76</v>
+        <v>9918</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>3251-1387-CM25</t>
+          <t>1467-26-CM25</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -8009,17 +8009,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>69.252.700-3</t>
+          <t>60.511.071-1</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PELLUHUE</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CURICÓ</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -8048,7 +8048,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>9918</v>
+        <v>2796.76</v>
       </c>
     </row>
     <row r="118">
@@ -8379,7 +8379,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>3385-90-CM25</t>
+          <t>3385-95-CM25</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -8438,13 +8438,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>3214.54</v>
+        <v>4286.05</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>3385-95-CM25</t>
+          <t>3385-90-CM25</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -8503,7 +8503,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>4286.05</v>
+        <v>3214.54</v>
       </c>
     </row>
     <row r="125">
@@ -8574,7 +8574,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>547641-149-CM25</t>
+          <t>4343-190-CM25</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -8594,17 +8594,17 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8633,13 +8633,13 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>365.89</v>
+        <v>24205.31</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>4343-190-CM25</t>
+          <t>547641-149-CM25</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -8659,17 +8659,17 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8698,13 +8698,13 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>24205.31</v>
+        <v>365.89</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2445-2843-CM25</t>
+          <t>707420-32-CM25</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -8763,13 +8763,13 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>72400.8</v>
+        <v>5528.3</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>707420-32-CM25</t>
+          <t>2445-2843-CM25</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -8794,12 +8794,12 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -8828,13 +8828,13 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>5528.3</v>
+        <v>72400.8</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>1978-499-CM25</t>
+          <t>1978-500-CM25</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -8893,13 +8893,13 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>1199.15</v>
+        <v>1346.62</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>1978-500-CM25</t>
+          <t>1978-499-CM25</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -8958,7 +8958,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1346.62</v>
+        <v>1199.15</v>
       </c>
     </row>
     <row r="132">
@@ -9224,7 +9224,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1199-163-CM25</t>
+          <t>1978-536-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -9244,17 +9244,17 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -9283,13 +9283,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>3517.07</v>
+        <v>45562.09</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>1978-536-CM25</t>
+          <t>1199-163-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -9309,17 +9309,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9348,7 +9348,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>45562.09</v>
+        <v>3517.07</v>
       </c>
     </row>
     <row r="138">
@@ -9419,7 +9419,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>1681-415-CM25</t>
+          <t>1681-416-CM25</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -9478,13 +9478,13 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>33248.63</v>
+        <v>46445.3</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>1681-416-CM25</t>
+          <t>1681-415-CM25</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -9543,7 +9543,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>46445.3</v>
+        <v>33248.63</v>
       </c>
     </row>
     <row r="141">
@@ -9809,7 +9809,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>1462-245-CM25</t>
+          <t>1465-1968-CM25</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>8112.18</v>
+        <v>14759.3</v>
       </c>
     </row>
     <row r="146">
@@ -9939,7 +9939,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1465-1968-CM25</t>
+          <t>1462-245-CM25</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9998,7 +9998,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>14759.3</v>
+        <v>8112.18</v>
       </c>
     </row>
     <row r="148">
@@ -11434,7 +11434,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1464-1020-CM25</t>
+          <t>2256-45-CM25</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11459,12 +11459,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>60.902.022-9</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -11493,13 +11493,13 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>30278.44</v>
+        <v>1284.99</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2256-45-CM25</t>
+          <t>1525-19-CM25</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11524,7 +11524,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>60.902.022-9</t>
+          <t>60.902.073-3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -11558,13 +11558,13 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>1284.99</v>
+        <v>1714.13</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1525-19-CM25</t>
+          <t>2127-31-CM25</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>60.902.073-3</t>
+          <t>60.902.050-4</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -11623,13 +11623,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>1714.13</v>
+        <v>856.98</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2127-31-CM25</t>
+          <t>1464-1020-CM25</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11654,12 +11654,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>60.902.050-4</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -11688,7 +11688,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>856.98</v>
+        <v>30278.44</v>
       </c>
     </row>
     <row r="174">
@@ -12409,7 +12409,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>3399-139-CM25</t>
+          <t>1057655-24-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12468,13 +12468,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2615.8</v>
+        <v>22435.38</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1057655-24-CM25</t>
+          <t>1978-760-CM25</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12494,17 +12494,17 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -12533,13 +12533,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>22435.38</v>
+        <v>3976.02</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1978-760-CM25</t>
+          <t>3399-139-CM25</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12559,17 +12559,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12598,7 +12598,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>3976.02</v>
+        <v>2615.8</v>
       </c>
     </row>
     <row r="188">
@@ -13189,7 +13189,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1391-1566-CM25</t>
+          <t>2436-873-CM25</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13209,17 +13209,17 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -13248,13 +13248,13 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4089.69</v>
+        <v>34324.74</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>2825-349-CM25</t>
+          <t>1391-1566-CM25</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13274,17 +13274,17 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>69.120.100-7</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -13313,13 +13313,13 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>8292.99</v>
+        <v>4089.69</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>2436-873-CM25</t>
+          <t>2825-349-CM25</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13344,12 +13344,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>69.120.100-7</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>I MUNICIPALIDAD DE CONSTITUCION</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -13378,13 +13378,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>34324.74</v>
+        <v>8292.99</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1173467-17-CM25</t>
+          <t>1057461-7338-CM25</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13409,12 +13409,12 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>61.946.900-3</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -13443,13 +13443,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1157.35</v>
+        <v>27732.09</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1057461-7338-CM25</t>
+          <t>1173467-17-CM25</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13474,12 +13474,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.946.900-3</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -13508,13 +13508,13 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>27732.09</v>
+        <v>1157.35</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1465-2108-CM25</t>
+          <t>3399-158-CM25</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13539,12 +13539,12 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -13573,13 +13573,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>13503.54</v>
+        <v>3204.2</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1057461-7383-CM25</t>
+          <t>1465-2108-CM25</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
@@ -13638,7 +13638,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>5835.68</v>
+        <v>13503.54</v>
       </c>
     </row>
     <row r="204">
@@ -13709,7 +13709,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>3399-158-CM25</t>
+          <t>1057461-7383-CM25</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13734,12 +13734,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13768,7 +13768,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3204.2</v>
+        <v>5835.68</v>
       </c>
     </row>
     <row r="206">
@@ -14294,7 +14294,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>3385-156-CM25</t>
+          <t>3385-157-CM25</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14353,13 +14353,13 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>630.01</v>
+        <v>4200.05</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>3385-157-CM25</t>
+          <t>2335-908-CM25</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14379,17 +14379,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14418,13 +14418,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>4200.05</v>
+        <v>1469.55</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>2335-908-CM25</t>
+          <t>3385-156-CM25</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
@@ -14483,7 +14483,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>1469.55</v>
+        <v>630.01</v>
       </c>
     </row>
     <row r="217">
@@ -14554,7 +14554,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1391-1720-CM25</t>
+          <t>1391-1717-CM25</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14613,13 +14613,13 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>8775.280000000001</v>
+        <v>237.45</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1391-1741-CM25</t>
+          <t>3385-162-CM25</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14644,12 +14644,12 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
@@ -14678,13 +14678,13 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3613.35</v>
+        <v>4129.54</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1391-1717-CM25</t>
+          <t>1391-1741-CM25</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14743,13 +14743,13 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>237.45</v>
+        <v>3613.35</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>3385-162-CM25</t>
+          <t>1391-1720-CM25</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -14808,7 +14808,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>4129.54</v>
+        <v>8775.280000000001</v>
       </c>
     </row>
     <row r="222">
@@ -15009,7 +15009,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>2046-396-CM25</t>
+          <t>1391-1736-CM25</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -15034,12 +15034,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -15068,13 +15068,13 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>18837.37</v>
+        <v>238.33</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1391-1736-CM25</t>
+          <t>2046-396-CM25</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -15099,12 +15099,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -15133,13 +15133,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>238.33</v>
+        <v>18837.37</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>3399-166-CM25</t>
+          <t>1469-2454-CM25</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -15159,17 +15159,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15198,13 +15198,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>2072.52</v>
+        <v>173.26</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1469-2454-CM25</t>
+          <t>3399-166-CM25</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15224,17 +15224,17 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -15263,13 +15263,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>173.26</v>
+        <v>2072.52</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1681-685-CM25</t>
+          <t>2045-293-CM25</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15294,12 +15294,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -15328,13 +15328,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>32450.36</v>
+        <v>7742.82</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1681-686-CM25</t>
+          <t>1681-685-CM25</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15393,13 +15393,13 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>46153.62</v>
+        <v>32450.36</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>2045-293-CM25</t>
+          <t>1681-686-CM25</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15424,12 +15424,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -15458,13 +15458,13 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>7742.82</v>
+        <v>46153.62</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1075337-13964-CM25</t>
+          <t>362-451-CM25</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -15489,12 +15489,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -15523,13 +15523,13 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>22166.83</v>
+        <v>8252.700000000001</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>362-451-CM25</t>
+          <t>1075337-13964-CM25</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -15554,12 +15554,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -15588,7 +15588,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>8252.700000000001</v>
+        <v>22166.83</v>
       </c>
     </row>
     <row r="234">
@@ -15659,7 +15659,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1057461-7633-CM25</t>
+          <t>1465-2160-CM25</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15684,12 +15684,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -15718,7 +15718,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>1353.39</v>
+        <v>12805.39</v>
       </c>
     </row>
     <row r="236">
@@ -15789,7 +15789,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1465-2160-CM25</t>
+          <t>1057461-7633-CM25</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -15814,12 +15814,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -15848,13 +15848,13 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>12805.39</v>
+        <v>1353.39</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>3399-170-CM25</t>
+          <t>1463-357-CM25</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -15879,12 +15879,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>61.946.800-7</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15913,13 +15913,13 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>3088.9</v>
+        <v>7781.19</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1463-357-CM25</t>
+          <t>3399-170-CM25</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -15944,12 +15944,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.946.800-7</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -15978,7 +15978,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>7781.19</v>
+        <v>3088.9</v>
       </c>
     </row>
     <row r="240">
@@ -16569,7 +16569,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1681-784-CM25</t>
+          <t>1057461-7747-CM25</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -16594,12 +16594,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16628,13 +16628,13 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>32926.23</v>
+        <v>35313.63</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1681-785-CM25</t>
+          <t>1681-784-CM25</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -16693,13 +16693,13 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>46575.56</v>
+        <v>32926.23</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1057461-7747-CM25</t>
+          <t>1681-785-CM25</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -16724,12 +16724,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>35313.63</v>
+        <v>46575.56</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>3385-196-CM25</t>
+          <t>1464-1490-CM25</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -16789,12 +16789,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -16823,7 +16823,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>484</v>
+        <v>29402.13</v>
       </c>
     </row>
     <row r="253">
@@ -16894,7 +16894,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1464-1490-CM25</t>
+          <t>3385-196-CM25</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -16919,12 +16919,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -16953,13 +16953,13 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>29402.13</v>
+        <v>484</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1511-7476-CM25</t>
+          <t>3385-202-CM25</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -16984,12 +16984,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -17018,13 +17018,13 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>80.92</v>
+        <v>4170.18</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1511-7478-CM25</t>
+          <t>1511-7474-CM25</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -17083,13 +17083,13 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>118.5</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1469-2886-CM25</t>
+          <t>1511-7476-CM25</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -17109,17 +17109,17 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -17148,13 +17148,13 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>8284.82</v>
+        <v>80.92</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1511-7474-CM25</t>
+          <t>1511-7478-CM25</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -17213,13 +17213,13 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>118.5</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>3385-202-CM25</t>
+          <t>1469-2886-CM25</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -17239,17 +17239,17 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -17278,13 +17278,13 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>4170.18</v>
+        <v>8284.82</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1075337-14366-CM25</t>
+          <t>1057461-7766-CM25</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -17309,12 +17309,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -17343,13 +17343,13 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>21691.31</v>
+        <v>2377.94</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1057461-7766-CM25</t>
+          <t>1075337-14366-CM25</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -17374,12 +17374,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -17408,7 +17408,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>2377.94</v>
+        <v>21691.31</v>
       </c>
     </row>
     <row r="262">
@@ -18194,7 +18194,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1978-1294-CM25</t>
+          <t>1462-448-CM25</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -18219,12 +18219,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -18253,13 +18253,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>3943.18</v>
+        <v>9117.91</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1469-3115-CM25</t>
+          <t>1978-1294-CM25</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -18279,17 +18279,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -18318,13 +18318,13 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>329.42</v>
+        <v>3943.18</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1462-448-CM25</t>
+          <t>1469-3115-CM25</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -18344,17 +18344,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -18383,7 +18383,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>9117.91</v>
+        <v>329.42</v>
       </c>
     </row>
     <row r="277">
@@ -18649,7 +18649,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>2335-6324-CM25</t>
+          <t>1978-1363-CM25</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -18674,12 +18674,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -18708,13 +18708,13 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>1066.41</v>
+        <v>55692.34</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1978-1363-CM25</t>
+          <t>2335-6324-CM25</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -18739,12 +18739,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -18773,7 +18773,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>55692.34</v>
+        <v>1066.41</v>
       </c>
     </row>
     <row r="283">
@@ -18844,7 +18844,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1057461-7911-CM25</t>
+          <t>3385-234-CM25</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -18869,12 +18869,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18903,13 +18903,13 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>32180.53</v>
+        <v>4247.95</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>3385-234-CM25</t>
+          <t>1681-863-CM25</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -18934,12 +18934,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -18968,13 +18968,13 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>4247.95</v>
+        <v>44510.16</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1681-863-CM25</t>
+          <t>1681-866-CM25</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -19033,13 +19033,13 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>44510.16</v>
+        <v>30056.84</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1681-866-CM25</t>
+          <t>1057461-7911-CM25</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -19064,12 +19064,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -19098,7 +19098,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>30056.84</v>
+        <v>32180.53</v>
       </c>
     </row>
     <row r="288">
@@ -19234,7 +19234,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1057461-7938-CM25</t>
+          <t>1465-2246-CM25</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -19259,12 +19259,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -19293,13 +19293,13 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>3021.44</v>
+        <v>13173.93</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1465-2246-CM25</t>
+          <t>1057461-7938-CM25</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -19324,12 +19324,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -19358,7 +19358,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>13173.93</v>
+        <v>3021.44</v>
       </c>
     </row>
     <row r="292">
@@ -19559,7 +19559,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>2046-511-CM25</t>
+          <t>2298-5205-CM25</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -19579,17 +19579,17 @@
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>69.110.100-2</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -19618,13 +19618,13 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>19258.52</v>
+        <v>13391.95</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>2298-5205-CM25</t>
+          <t>2046-511-CM25</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -19644,17 +19644,17 @@
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>69.110.100-2</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -19683,7 +19683,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>13391.95</v>
+        <v>19258.52</v>
       </c>
     </row>
     <row r="297">
@@ -19819,7 +19819,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1391-2271-CM25</t>
+          <t>4452-989-CC25</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19844,12 +19844,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19878,13 +19878,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>2134.71</v>
+        <v>28615.8</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>4452-989-CC25</t>
+          <t>362-513-CM25</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19909,12 +19909,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19943,13 +19943,13 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>28615.8</v>
+        <v>9049.889999999999</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>362-513-CM25</t>
+          <t>1391-2271-CM25</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -19974,12 +19974,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -20008,7 +20008,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>9049.889999999999</v>
+        <v>2134.71</v>
       </c>
     </row>
     <row r="302">
@@ -20664,7 +20664,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1596-355-CM25</t>
+          <t>362-554-CM25</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -20684,17 +20684,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>72.227.000-2</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL VII REGION</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20723,7 +20723,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>4159.46</v>
+        <v>9108.219999999999</v>
       </c>
     </row>
     <row r="313">
@@ -20794,7 +20794,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1681-956-CM25</t>
+          <t>2045-392-CM25</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -20819,12 +20819,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -20853,13 +20853,13 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>48247.75</v>
+        <v>6982.56</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>362-554-CM25</t>
+          <t>1681-956-CM25</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -20884,12 +20884,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -20918,13 +20918,13 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>9108.219999999999</v>
+        <v>48247.75</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>2045-392-CM25</t>
+          <t>1596-355-CM25</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -20944,17 +20944,17 @@
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>72.227.000-2</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>GOBIERNO REGIONAL VII REGION</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>6982.56</v>
+        <v>4159.46</v>
       </c>
     </row>
     <row r="317">
@@ -21379,7 +21379,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>4452-1031-CC25</t>
+          <t>1511-7723-CM25</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -21404,12 +21404,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>62787.75</v>
+        <v>22040.76</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>1511-7723-CM25</t>
+          <t>4452-1031-CC25</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -21469,12 +21469,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -21503,13 +21503,13 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>22040.76</v>
+        <v>62787.75</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>1057461-8056-CM25</t>
+          <t>1057655-3406-CM25</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -21534,12 +21534,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -21568,13 +21568,13 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>2120.13</v>
+        <v>24088.48</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1057655-3406-CM25</t>
+          <t>1057461-8056-CM25</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -21599,12 +21599,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -21633,7 +21633,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>24088.48</v>
+        <v>2120.13</v>
       </c>
     </row>
     <row r="327">
@@ -22549,7 +22549,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>1464-8508-CM25</t>
+          <t>1681-1023-CM25</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22574,12 +22574,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22608,13 +22608,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>31017.47</v>
+        <v>33078.48</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1681-1023-CM25</t>
+          <t>1464-8508-CM25</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22639,12 +22639,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -22673,7 +22673,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>33078.48</v>
+        <v>31017.47</v>
       </c>
     </row>
     <row r="343">
@@ -23914,7 +23914,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>1681-84-CM26</t>
+          <t>1464-141-CM26</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -23939,12 +23939,12 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G362" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
@@ -23973,13 +23973,13 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>45392.74</v>
+        <v>32941.9</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>1681-85-CM26</t>
+          <t>5052-91-SE26</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -24004,12 +24004,12 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -24038,13 +24038,13 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>34100.79</v>
+        <v>208638.41</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>5052-91-SE26</t>
+          <t>1681-84-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -24069,12 +24069,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -24103,13 +24103,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>208638.41</v>
+        <v>45392.74</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>1464-141-CM26</t>
+          <t>1681-85-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -24134,12 +24134,12 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -24168,13 +24168,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>32941.9</v>
+        <v>34100.79</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>1075337-6524-CM26</t>
+          <t>1465-57-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -24199,12 +24199,12 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -24233,13 +24233,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>30288.89</v>
+        <v>14651.66</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>1465-57-CM26</t>
+          <t>3385-15-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -24264,12 +24264,12 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G367" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H367" t="inlineStr">
@@ -24298,13 +24298,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>14651.66</v>
+        <v>3593.69</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>3385-15-CM26</t>
+          <t>1075337-6524-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -24329,12 +24329,12 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G368" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H368" t="inlineStr">
@@ -24363,13 +24363,13 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>3593.69</v>
+        <v>30288.89</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>1391-187-CM26</t>
+          <t>1057461-222-CM26</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -24394,12 +24394,12 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>61.004.051-9</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -24428,13 +24428,13 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>46237.43</v>
+        <v>32492.81</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>1057461-222-CM26</t>
+          <t>1391-187-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -24459,12 +24459,12 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.004.051-9</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -24493,7 +24493,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>32492.81</v>
+        <v>46237.43</v>
       </c>
     </row>
     <row r="371">
@@ -25084,7 +25084,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>1681-159-CM26</t>
+          <t>5052-147-SE26</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -25109,12 +25109,12 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G380" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H380" t="inlineStr">
@@ -25143,13 +25143,13 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>48458.71</v>
+        <v>304530.39</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>1978-150-CM26</t>
+          <t>1681-156-CM26</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -25174,12 +25174,12 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H381" t="inlineStr">
@@ -25208,13 +25208,13 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>60927.26</v>
+        <v>37402.25</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>5052-147-SE26</t>
+          <t>1978-150-CM26</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -25239,12 +25239,12 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H382" t="inlineStr">
@@ -25273,13 +25273,13 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>304530.39</v>
+        <v>60927.26</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>1681-156-CM26</t>
+          <t>1681-159-CM26</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -25338,7 +25338,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>37402.25</v>
+        <v>48458.71</v>
       </c>
     </row>
     <row r="384">
@@ -25474,7 +25474,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>1057461-327-CM26</t>
+          <t>1465-108-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -25499,12 +25499,12 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G386" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H386" t="inlineStr">
@@ -25533,13 +25533,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>36003.74</v>
+        <v>14607.2</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>1465-108-CM26</t>
+          <t>1057461-327-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -25564,12 +25564,12 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -25598,13 +25598,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>14607.2</v>
+        <v>36003.74</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>1463-104-CM26</t>
+          <t>1462-72-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -25629,12 +25629,12 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -25663,13 +25663,13 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>8546.9</v>
+        <v>9244.719999999999</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>1462-72-CM26</t>
+          <t>1142-61-CM26</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -25694,12 +25694,12 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>60.511.070-3</t>
         </is>
       </c>
       <c r="G389" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
         </is>
       </c>
       <c r="H389" t="inlineStr">
@@ -25728,13 +25728,13 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>9244.719999999999</v>
+        <v>2035.71</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>1142-61-CM26</t>
+          <t>1463-104-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -25759,12 +25759,12 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>60.511.070-3</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -25793,7 +25793,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2035.71</v>
+        <v>8546.9</v>
       </c>
     </row>
     <row r="391">
@@ -25929,7 +25929,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>1057461-344-CM26</t>
+          <t>5052-255-SE26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25954,12 +25954,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25988,13 +25988,13 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>5618.98</v>
+        <v>237775.48</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>5052-255-SE26</t>
+          <t>1057461-344-CM26</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -26019,12 +26019,12 @@
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -26053,7 +26053,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>237775.48</v>
+        <v>5618.98</v>
       </c>
     </row>
     <row r="395">
@@ -26124,7 +26124,7 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>1199-61-CM26</t>
+          <t>4343-79-CM26</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -26149,12 +26149,12 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -26183,13 +26183,13 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>7260.99</v>
+        <v>25299.6</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>4343-79-CM26</t>
+          <t>1199-61-CM26</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -26214,12 +26214,12 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G397" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H397" t="inlineStr">
@@ -26248,13 +26248,13 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>25299.6</v>
+        <v>7260.99</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>2436-296-CM26</t>
+          <t>362-195-CM26</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -26274,17 +26274,17 @@
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G398" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H398" t="inlineStr">
@@ -26313,13 +26313,13 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>33936.98</v>
+        <v>8207.26</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>362-195-CM26</t>
+          <t>1738-95-CM26</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -26339,17 +26339,17 @@
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.130.200-8</t>
         </is>
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -26378,13 +26378,13 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>8207.26</v>
+        <v>23715.5</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>1738-95-CM26</t>
+          <t>2436-296-CM26</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -26409,12 +26409,12 @@
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>69.130.200-8</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEGRE</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -26443,7 +26443,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>23715.5</v>
+        <v>33936.98</v>
       </c>
     </row>
     <row r="401">
@@ -26644,7 +26644,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>1469-586-CM26</t>
+          <t>1681-246-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -26664,17 +26664,17 @@
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -26703,7 +26703,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>367.78</v>
+        <v>28448.72</v>
       </c>
     </row>
     <row r="405">
@@ -26774,7 +26774,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>1681-246-CM26</t>
+          <t>1469-586-CM26</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -26794,17 +26794,17 @@
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -26833,7 +26833,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>28448.72</v>
+        <v>367.78</v>
       </c>
     </row>
     <row r="407">
@@ -26969,7 +26969,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>1978-256-CM26</t>
+          <t>1462-119-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26994,12 +26994,12 @@
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -27028,13 +27028,13 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>56336.66</v>
+        <v>8954.35</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>1462-119-CM26</t>
+          <t>1978-256-CM26</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -27059,12 +27059,12 @@
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -27093,13 +27093,13 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>8954.35</v>
+        <v>56336.66</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>1057461-450-CM26</t>
+          <t>1511-416-CM26</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -27124,12 +27124,12 @@
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G411" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H411" t="inlineStr">
@@ -27158,13 +27158,13 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>28559.97</v>
+        <v>26437.99</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>1511-416-CM26</t>
+          <t>1057461-450-CM26</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -27189,12 +27189,12 @@
       </c>
       <c r="F412" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G412" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H412" t="inlineStr">
@@ -27223,7 +27223,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>26437.99</v>
+        <v>28559.97</v>
       </c>
     </row>
     <row r="413">
@@ -27294,7 +27294,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>2046-141-CM26</t>
+          <t>1465-142-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,12 +27319,12 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.606.908-k</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>18822.4</v>
+        <v>14569.51</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>1465-142-CM26</t>
+          <t>2046-141-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27384,12 +27384,12 @@
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.908-k</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>14569.51</v>
+        <v>18822.4</v>
       </c>
     </row>
     <row r="416">
@@ -27879,7 +27879,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>2436-425-CM26</t>
+          <t>2436-428-CM26</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -27938,7 +27938,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>17263.27</v>
+        <v>17188.86</v>
       </c>
     </row>
     <row r="424">
@@ -28009,7 +28009,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>2436-427-CM26</t>
+          <t>2436-425-CM26</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -28068,13 +28068,13 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>40677.81</v>
+        <v>17263.27</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>2436-428-CM26</t>
+          <t>2436-427-CM26</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -28133,7 +28133,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>17188.86</v>
+        <v>40677.81</v>
       </c>
     </row>
     <row r="427">
@@ -28269,7 +28269,7 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>1978-349-CM26</t>
+          <t>2045-134-CM26</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -28294,12 +28294,12 @@
       </c>
       <c r="F429" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G429" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H429" t="inlineStr">
@@ -28328,13 +28328,13 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>58564.41</v>
+        <v>6725.1</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>2045-134-CM26</t>
+          <t>1978-349-CM26</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -28359,12 +28359,12 @@
       </c>
       <c r="F430" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -28393,7 +28393,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>6725.1</v>
+        <v>58564.41</v>
       </c>
     </row>
     <row r="431">
@@ -29699,7 +29699,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1681-394-CM26</t>
+          <t>1681-395-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29758,13 +29758,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>36650.37</v>
+        <v>50076.96</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>1681-395-CM26</t>
+          <t>1469-1396-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29784,17 +29784,17 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>50076.96</v>
+        <v>1341.1</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>1469-1396-CM26</t>
+          <t>1681-394-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29849,17 +29849,17 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -29888,7 +29888,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>1341.1</v>
+        <v>36650.37</v>
       </c>
     </row>
     <row r="454">
@@ -30089,7 +30089,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1199-126-CM26</t>
+          <t>1462-197-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30114,12 +30114,12 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
@@ -30148,13 +30148,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>13508.04</v>
+        <v>8959.639999999999</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>1463-226-CM26</t>
+          <t>1199-126-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30179,12 +30179,12 @@
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
@@ -30213,7 +30213,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>8506.969999999999</v>
+        <v>13508.04</v>
       </c>
     </row>
     <row r="459">
@@ -30284,7 +30284,7 @@
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>1465-220-CM26</t>
+          <t>1463-226-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -30309,12 +30309,12 @@
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
@@ -30343,13 +30343,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>14981.46</v>
+        <v>8506.969999999999</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>1462-197-CM26</t>
+          <t>1465-220-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -30374,12 +30374,12 @@
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
@@ -30408,7 +30408,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>8959.639999999999</v>
+        <v>14981.46</v>
       </c>
     </row>
     <row r="462">
@@ -30609,7 +30609,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>4343-197-CM26</t>
+          <t>4343-196-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30668,13 +30668,13 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>24838.24</v>
+        <v>396.8</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>4343-196-CM26</t>
+          <t>4343-197-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -30733,7 +30733,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>396.8</v>
+        <v>24838.24</v>
       </c>
     </row>
     <row r="467">
@@ -30869,7 +30869,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2333-333-CM26</t>
+          <t>2045-208-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30894,12 +30894,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>69.130.300-4</t>
+          <t>61.606.910-1</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30928,13 +30928,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>2030.11</v>
+        <v>10151.94</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>2045-208-CM26</t>
+          <t>707420-101-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30959,12 +30959,12 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>61.606.910-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CUREPTO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -30993,13 +30993,13 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>10151.94</v>
+        <v>14740.62</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>707420-101-CM26</t>
+          <t>362-341-CM26</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -31024,12 +31024,12 @@
       </c>
       <c r="F471" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G471" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H471" t="inlineStr">
@@ -31058,13 +31058,13 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>14740.62</v>
+        <v>8926.379999999999</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>362-341-CM26</t>
+          <t>2333-333-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31089,12 +31089,12 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>69.130.300-4</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
@@ -31123,7 +31123,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>8926.379999999999</v>
+        <v>2030.11</v>
       </c>
     </row>
     <row r="473">
@@ -31454,7 +31454,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>1681-471-CM26</t>
+          <t>1681-472-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -31513,13 +31513,13 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>48250.67</v>
+        <v>35358.32</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>1681-472-CM26</t>
+          <t>1681-471-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -31578,18 +31578,18 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>35358.32</v>
+        <v>48250.67</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>4452-547-SE26</t>
+          <t>1681-482-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -31609,12 +31609,12 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -31643,7 +31643,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>165633.96</v>
+        <v>109.65</v>
       </c>
     </row>
     <row r="481">
@@ -31714,12 +31714,12 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>1681-482-CM26</t>
+          <t>4452-547-SE26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -31739,12 +31739,12 @@
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -31773,7 +31773,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>109.65</v>
+        <v>165633.96</v>
       </c>
     </row>
     <row r="483">
@@ -31844,7 +31844,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>1463-255-CM26</t>
+          <t>1465-276-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31869,12 +31869,12 @@
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
@@ -31903,13 +31903,13 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>8406.639999999999</v>
+        <v>15172.85</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>1462-241-CM26</t>
+          <t>1463-255-CM26</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -31934,12 +31934,12 @@
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
@@ -31968,13 +31968,13 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>9215.5</v>
+        <v>8406.639999999999</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1465-276-CM26</t>
+          <t>1462-241-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31999,12 +31999,12 @@
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -32033,13 +32033,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>15172.85</v>
+        <v>9215.5</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>3385-161-CM26</t>
+          <t>1057461-969-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -32064,12 +32064,12 @@
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
@@ -32098,13 +32098,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>867.96</v>
+        <v>2763.79</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1057461-969-CM26</t>
+          <t>3385-160-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32129,12 +32129,12 @@
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -32163,13 +32163,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>2763.79</v>
+        <v>867.96</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>3385-160-CM26</t>
+          <t>3385-161-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32624,7 +32624,7 @@
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>1978-716-CM26</t>
+          <t>2335-602-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32649,12 +32649,12 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
@@ -32683,13 +32683,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>6358.27</v>
+        <v>868.87</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>2335-602-CM26</t>
+          <t>1978-716-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32748,7 +32748,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>868.87</v>
+        <v>6358.27</v>
       </c>
     </row>
     <row r="498">
@@ -33079,7 +33079,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>1681-560-CM26</t>
+          <t>1681-561-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -33138,13 +33138,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>50338.9</v>
+        <v>38138.1</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>1681-561-CM26</t>
+          <t>1681-560-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33203,7 +33203,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>38138.1</v>
+        <v>50338.9</v>
       </c>
     </row>
     <row r="505">
@@ -33274,12 +33274,12 @@
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>4452-672-SE26</t>
+          <t>1978-786-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -33294,17 +33294,17 @@
       </c>
       <c r="E506" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -33333,13 +33333,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>159487.73</v>
+        <v>73324.28</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>1978-786-CM26</t>
+          <t>1978-787-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>73324.28</v>
+        <v>15712.35</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>1978-787-CM26</t>
+          <t>1464-1163-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33424,17 +33424,17 @@
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -33463,18 +33463,18 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>15712.35</v>
+        <v>37395.38</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>1464-1163-CM26</t>
+          <t>4452-672-SE26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -33494,12 +33494,12 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
@@ -33528,13 +33528,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>37395.38</v>
+        <v>159487.73</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>1463-278-CM26</t>
+          <t>1057461-1219-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33559,12 +33559,12 @@
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>61.606.905-5</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -33593,13 +33593,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>9500.01</v>
+        <v>36596.6</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1057461-1219-CM26</t>
+          <t>1463-278-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33624,12 +33624,12 @@
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.905-5</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
@@ -33658,13 +33658,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>36596.6</v>
+        <v>9500.01</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>1465-366-CM26</t>
+          <t>2335-648-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33684,17 +33684,17 @@
       </c>
       <c r="E512" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.606.907-1</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -33723,13 +33723,13 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>14079.24</v>
+        <v>271.09</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>2335-648-CM26</t>
+          <t>2335-647-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33788,13 +33788,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>271.09</v>
+        <v>1084.38</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>2335-647-CM26</t>
+          <t>2335-645-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33853,13 +33853,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>1084.38</v>
+        <v>108.44</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>2335-645-CM26</t>
+          <t>2335-646-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33918,7 +33918,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>108.44</v>
+        <v>542.1900000000001</v>
       </c>
     </row>
     <row r="516">
@@ -33989,7 +33989,7 @@
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2335-646-CM26</t>
+          <t>1465-366-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -34009,17 +34009,17 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.907-1</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
@@ -34048,7 +34048,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>542.1900000000001</v>
+        <v>14079.24</v>
       </c>
     </row>
     <row r="518">
@@ -34379,12 +34379,12 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>4343-265-CM26</t>
+          <t>4452-746-SE26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -34404,12 +34404,12 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -34438,18 +34438,18 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>24014.51</v>
+        <v>28678.33</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>4452-746-SE26</t>
+          <t>4343-264-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -34469,12 +34469,12 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>28678.33</v>
+        <v>127.3</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4343-264-CM26</t>
+          <t>4343-265-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34568,7 +34568,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>127.3</v>
+        <v>24014.51</v>
       </c>
     </row>
     <row r="526">
@@ -34639,7 +34639,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>1511-987-CM26</t>
+          <t>1511-991-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34698,7 +34698,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>214.4</v>
+        <v>92.19</v>
       </c>
     </row>
     <row r="528">
@@ -34834,7 +34834,7 @@
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1511-990-CM26</t>
+          <t>1511-987-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34893,13 +34893,13 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>107.2</v>
+        <v>214.4</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>1511-991-CM26</t>
+          <t>1978-893-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -34919,17 +34919,17 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -34958,13 +34958,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>92.19</v>
+        <v>1177.1</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>1978-893-CM26</t>
+          <t>1511-990-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34984,17 +34984,17 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -35023,7 +35023,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>1177.1</v>
+        <v>107.2</v>
       </c>
     </row>
     <row r="533">
@@ -35159,12 +35159,12 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>1681-624-CM26</t>
+          <t>5052-637-SE26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2239-1-LR26</t>
+          <t>2239-13-LR23</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -35184,12 +35184,12 @@
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -35218,13 +35218,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>53236.72</v>
+        <v>274006.67</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>1681-623-CM26</t>
+          <t>2335-677-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35244,17 +35244,17 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>69.130.301-2</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>I MUNICIPALIDAD DE LINARES</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -35283,13 +35283,13 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>39191.68</v>
+        <v>107.93</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>5052-637-SE26</t>
+          <t>4452-779-SE26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -35314,12 +35314,12 @@
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
@@ -35348,13 +35348,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>274006.67</v>
+        <v>160327.63</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>2335-677-CM26</t>
+          <t>1681-623-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35374,17 +35374,17 @@
       </c>
       <c r="E538" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>69.130.301-2</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LINARES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
@@ -35413,18 +35413,18 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>107.93</v>
+        <v>39191.68</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>4452-779-SE26</t>
+          <t>1681-624-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2239-13-LR23</t>
+          <t>2239-1-LR26</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -35444,12 +35444,12 @@
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
@@ -35478,7 +35478,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>160327.63</v>
+        <v>53236.72</v>
       </c>
     </row>
     <row r="540">
@@ -35744,7 +35744,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1978-957-CM26</t>
+          <t>1464-1326-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35764,17 +35764,17 @@
       </c>
       <c r="E544" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>61.606.900-4</t>
+          <t>61.606.918-7</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
@@ -35803,13 +35803,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>630.66</v>
+        <v>37652.55</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>1464-1326-CM26</t>
+          <t>1079566-332-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35834,12 +35834,12 @@
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>61.606.918-7</t>
+          <t>61.979.370-6</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE PARRAL</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
@@ -35849,12 +35849,12 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>76.032.107-9</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
@@ -35868,13 +35868,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>37652.55</v>
+        <v>521758.93</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>4605-94-CM26</t>
+          <t>1978-957-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35894,17 +35894,17 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>61.819.000-5</t>
+          <t>61.606.900-4</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>2438.44</v>
+        <v>630.66</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>1079566-332-CM26</t>
+          <t>4605-94-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35964,12 +35964,12 @@
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>61.979.370-6</t>
+          <t>61.819.000-5</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION VII REGION</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
@@ -35979,12 +35979,12 @@
       </c>
       <c r="I547" t="inlineStr">
         <is>
-          <t>FDD INNOVACION &amp; CRECIMIENTO S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J547" t="inlineStr">
         <is>
-          <t>76.032.107-9</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K547" t="inlineStr">
@@ -35998,7 +35998,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>521758.93</v>
+        <v>2438.44</v>
       </c>
     </row>
     <row r="548">
@@ -36069,7 +36069,7 @@
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>1057461-1426-CM26</t>
+          <t>362-490-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -36094,12 +36094,12 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.915-2</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -36128,13 +36128,13 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>38854.17</v>
+        <v>9058.23</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>362-490-CM26</t>
+          <t>1057461-1426-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -36159,12 +36159,12 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>61.606.915-2</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
@@ -36193,13 +36193,13 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>9058.23</v>
+        <v>38854.17</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>3385-204-CM26</t>
+          <t>1075337-9601-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36224,12 +36224,12 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>61.101.023-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
@@ -36258,13 +36258,13 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>524.9</v>
+        <v>29280.54</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>1075337-9601-CM26</t>
+          <t>1462-349-CM26</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -36289,12 +36289,12 @@
       </c>
       <c r="F552" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.606.906-3</t>
         </is>
       </c>
       <c r="G552" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
         </is>
       </c>
       <c r="H552" t="inlineStr">
@@ -36323,13 +36323,13 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>29280.54</v>
+        <v>9231.26</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>1462-349-CM26</t>
+          <t>707420-124-CM26</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -36354,12 +36354,12 @@
       </c>
       <c r="F553" t="inlineStr">
         <is>
-          <t>61.606.906-3</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G553" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H553" t="inlineStr">
@@ -36388,13 +36388,13 @@
         </is>
       </c>
       <c r="M553" s="2" t="n">
-        <v>9231.26</v>
+        <v>715.15</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>707420-124-CM26</t>
+          <t>3385-204-CM26</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -36419,12 +36419,12 @@
       </c>
       <c r="F554" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.101.023-0</t>
         </is>
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -36453,7 +36453,7 @@
         </is>
       </c>
       <c r="M554" s="2" t="n">
-        <v>715.15</v>
+        <v>524.9</v>
       </c>
     </row>
     <row r="555">
@@ -36524,7 +36524,7 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>1057461-1474-CM26</t>
+          <t>4343-267-CM26</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
@@ -36549,12 +36549,12 @@
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>61.606.912-8</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -36583,13 +36583,13 @@
         </is>
       </c>
       <c r="M556" s="2" t="n">
-        <v>6182.7</v>
+        <v>974.47</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>2294-1788-CM26</t>
+          <t>2294-1786-CM26</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -36648,13 +36648,13 @@
         </is>
       </c>
       <c r="M557" s="2" t="n">
-        <v>37020.58</v>
+        <v>32519.85</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>1511-1057-CM26</t>
+          <t>2294-1788-CM26</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -36674,17 +36674,17 @@
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>61.606.911-k</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
         <is>
-          <t>Hospital de Constitución</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H558" t="inlineStr">
@@ -36694,12 +36694,12 @@
       </c>
       <c r="I558" t="inlineStr">
         <is>
-          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
         </is>
       </c>
       <c r="J558" t="inlineStr">
         <is>
-          <t>96.781.350-8</t>
+          <t>96.556.930-8</t>
         </is>
       </c>
       <c r="K558" t="inlineStr">
@@ -36713,13 +36713,13 @@
         </is>
       </c>
       <c r="M558" s="2" t="n">
-        <v>24839.36</v>
+        <v>37020.58</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>4343-267-CM26</t>
+          <t>1511-1057-CM26</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -36744,12 +36744,12 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>61.606.912-8</t>
+          <t>61.606.911-k</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -36778,13 +36778,13 @@
         </is>
       </c>
       <c r="M559" s="2" t="n">
-        <v>974.47</v>
+        <v>24839.36</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>2294-1786-CM26</t>
+          <t>1057461-1474-CM26</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -36804,17 +36804,17 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -36824,12 +36824,12 @@
       </c>
       <c r="I560" t="inlineStr">
         <is>
-          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J560" t="inlineStr">
         <is>
-          <t>96.556.930-8</t>
+          <t>96.781.350-8</t>
         </is>
       </c>
       <c r="K560" t="inlineStr">
@@ -36843,7 +36843,7 @@
         </is>
       </c>
       <c r="M560" s="2" t="n">
-        <v>32519.85</v>
+        <v>6182.7</v>
       </c>
     </row>
     <row r="561">
@@ -38169,7 +38169,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -38234,7 +38234,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -38299,7 +38299,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -38339,6 +38339,2086 @@
       </c>
       <c r="M583" s="2" t="n">
         <v>452.21</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>1057461-1623-CM26</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J584" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M584" s="2" t="n">
+        <v>39213.67</v>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2294-2078-CM26</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M585" s="2" t="n">
+        <v>7257.28</v>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>3399-192-CM26</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>61.946.800-7</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M586" s="2" t="n">
+        <v>520.36</v>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>1978-1088-CM26</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>61.606.900-4</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M587" s="2" t="n">
+        <v>595.63</v>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>1462-414-CM26</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>61.606.906-3</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE HUALANE</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M588" s="2" t="n">
+        <v>9371.58</v>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>1465-499-CM26</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>61.606.907-1</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TENO</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M589" s="2" t="n">
+        <v>15146.15</v>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>1469-2962-CM26</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>70.885.500-6</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M590" s="2" t="n">
+        <v>11983.05</v>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>1681-754-CM26</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>61.606.917-9</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M591" s="2" t="n">
+        <v>734.39</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>4343-319-CM26</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>61.606.912-8</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL SAN JAVIER</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M592" s="2" t="n">
+        <v>25385.35</v>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>1463-408-CM26</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>61.606.905-5</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LICANTEN</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M593" s="2" t="n">
+        <v>9179.85</v>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>1511-1191-CM26</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>61.606.911-k</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>Hospital de Constitución</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M594" s="2" t="n">
+        <v>24079.57</v>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>2310-794-CM26</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>69.110.100-2</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M595" s="2" t="n">
+        <v>57835.66</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>362-545-CM26</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>61.606.915-2</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M596" s="2" t="n">
+        <v>8114.77</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>1057461-1669-CM26</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>61.606.913-6</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M597" s="2" t="n">
+        <v>4830.54</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2294-2178-CM26</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M598" s="2" t="n">
+        <v>14319.57</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>1511-1237-CM26</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>61.606.911-k</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>Hospital de Constitución</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M599" s="2" t="n">
+        <v>99.84</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>1511-1204-CM26</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>61.606.911-k</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>Hospital de Constitución</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M600" s="2" t="n">
+        <v>44.93</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>1511-1205-CM26</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>61.606.911-k</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>Hospital de Constitución</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M601" s="2" t="n">
+        <v>89.84999999999999</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2294-2225-CM26</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M602" s="2" t="n">
+        <v>33926.69</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>1391-2032-CM26</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>61.004.051-9</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J603" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M603" s="2" t="n">
+        <v>700.7</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>4452-934-CM26</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>61.606.903-9</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J604" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M604" s="2" t="n">
+        <v>34329.69</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2046-496-CM26</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>61.606.908-k</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE MOLINA</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J605" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M605" s="2" t="n">
+        <v>18911.75</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>1978-1129-CM26</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>61.606.900-4</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL MAULE</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M606" s="2" t="n">
+        <v>6994.36</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2294-1918-CM26</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M607" s="2" t="n">
+        <v>44339.11</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2294-2287-CM26</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M608" s="2" t="n">
+        <v>32609.74</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>691-21-CM26</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>61.802.007-K</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>SUBSECRETARIA DEL MINISTERIO DE LA VIVIENDA Y URBANISMO</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M609" s="2" t="n">
+        <v>1148.27</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2445-2554-CM26</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>69.100.100-8</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CURICO</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M610" s="2" t="n">
+        <v>52096.12</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2294-2243-CM26</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M611" s="2" t="n">
+        <v>407.39</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2294-2242-CM26</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M612" s="2" t="n">
+        <v>12166.88</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2294-2219-CM26</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M613" s="2" t="n">
+        <v>4784.13</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2047-92-CM26</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>60.511.073-8</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE LINARES</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>EDENRED CHILE SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>96.781.350-8</t>
+        </is>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M614" s="2" t="n">
+        <v>902.4400000000001</v>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2294-2240-CM26</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>2239-1-LR26</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>69.110.400-1</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE TALCA</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>SODEXO SOLUCIONES DE MOTIVACION CHILE S.A.</t>
+        </is>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>96.556.930-8</t>
+        </is>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M615" s="2" t="n">
+        <v>153.29</v>
       </c>
     </row>
   </sheetData>
